--- a/DATA_INPUT/annotation/ANNOTATION_FILE_public.xlsx
+++ b/DATA_INPUT/annotation/ANNOTATION_FILE_public.xlsx
@@ -1,784 +1,791 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Spoiler\SPOILER_Submission\DATA_INPUT\annotation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965E4F72-F12A-4860-9FC1-8E6DE7B16395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="140" yWindow="0" windowWidth="18380" windowHeight="15280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
-  <si>
-    <t xml:space="preserve">Sample_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">slide name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Segment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">area</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nuclei</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No Template Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stroma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear cell carcinoma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epithelial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PanCK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-A12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-B12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cancer-like endometriosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-C12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-D12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simple endometriosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-E12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endometrioid carcinoma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-G12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660013638-C-H12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atypical Epithelial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atypical endometriosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-A12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-B12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-C12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-D12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-E12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scan_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-G12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pt_14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DSP-1001660015487-D-H12</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="253">
+  <si>
+    <t>Sample_ID</t>
+  </si>
+  <si>
+    <t>slide name</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>roi</t>
+  </si>
+  <si>
+    <t>Scan_ID</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>Patient_ID</t>
+  </si>
+  <si>
+    <t>nuclei</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A01</t>
+  </si>
+  <si>
+    <t>No Template Control</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A02</t>
+  </si>
+  <si>
+    <t>Scan_01</t>
+  </si>
+  <si>
+    <t>CD68</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>Stroma</t>
+  </si>
+  <si>
+    <t>Clear cell carcinoma</t>
+  </si>
+  <si>
+    <t>Pt_01</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A03</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A04</t>
+  </si>
+  <si>
+    <t>CD3</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Epithelial</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A05</t>
+  </si>
+  <si>
+    <t>PanCK</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A06</t>
+  </si>
+  <si>
+    <t>004</t>
+  </si>
+  <si>
+    <t>Cancer</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A07</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A08</t>
+  </si>
+  <si>
+    <t>005</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A09</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A10</t>
+  </si>
+  <si>
+    <t>006</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A11</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-A12</t>
+  </si>
+  <si>
+    <t>007</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B01</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B02</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B03</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B04</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B05</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B06</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B07</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B08</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B09</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B10</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B11</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-B12</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C01</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C02</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C03</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C04</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C05</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C06</t>
+  </si>
+  <si>
+    <t>Scan_02</t>
+  </si>
+  <si>
+    <t>Pt_02</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C07</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C08</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C09</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C10</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C11</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-C12</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D01</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D02</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D03</t>
+  </si>
+  <si>
+    <t>Pt_03</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D04</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D05</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D06</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D07</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D08</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D09</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D10</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D11</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-D12</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E01</t>
+  </si>
+  <si>
+    <t>Scan_03</t>
+  </si>
+  <si>
+    <t>Simple endometriosis</t>
+  </si>
+  <si>
+    <t>Pt_04</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E02</t>
+  </si>
+  <si>
+    <t>Pt_05</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E03</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E04</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E05</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E06</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E07</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E08</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E09</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E10</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E11</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-E12</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F01</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F02</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F03</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F04</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F05</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F06</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F07</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F08</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F09</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F10</t>
+  </si>
+  <si>
+    <t>Scan_04</t>
+  </si>
+  <si>
+    <t>Endometrioid carcinoma</t>
+  </si>
+  <si>
+    <t>Pt_06</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F11</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-F12</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G01</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G02</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G03</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G04</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G05</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G06</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G07</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G08</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G09</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G10</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G11</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-G12</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H01</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H02</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H03</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H04</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H05</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H06</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H07</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H08</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H09</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H10</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H11</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>DSP-1001660013638-C-H12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A02</t>
+  </si>
+  <si>
+    <t>Scan_05</t>
+  </si>
+  <si>
+    <t>Atypical Epithelial</t>
+  </si>
+  <si>
+    <t>Atypical endometriosis</t>
+  </si>
+  <si>
+    <t>Pt_07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A05</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A06</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A09</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-A12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B02</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B05</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B06</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B09</t>
+  </si>
+  <si>
+    <t>Pt_08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-B12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C02</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C05</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C06</t>
+  </si>
+  <si>
+    <t>Scan_06</t>
+  </si>
+  <si>
+    <t>Pt_09</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C09</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-C12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D02</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D05</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D06</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D09</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D11</t>
+  </si>
+  <si>
+    <t>Pt_10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-D12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E02</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E05</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E06</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E09</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-E12</t>
+  </si>
+  <si>
+    <t>Scan_07</t>
+  </si>
+  <si>
+    <t>Pt_11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F02</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F05</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F06</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F08</t>
+  </si>
+  <si>
+    <t>Pt_12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F09</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-F12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G02</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G05</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G06</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G09</t>
+  </si>
+  <si>
+    <t>Scan_08</t>
+  </si>
+  <si>
+    <t>Pt_13</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-G12</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H01</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H02</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H03</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H04</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H05</t>
+  </si>
+  <si>
+    <t>Pt_14</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H06</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H07</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H08</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H09</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H10</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H11</t>
+  </si>
+  <si>
+    <t>DSP-1001660015487-D-H12</t>
+  </si>
+  <si>
+    <t>Endometriosis CLE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -814,6 +821,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1095,11 +1111,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J193"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1131,23 +1147,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2"/>
-      <c r="D2"/>
-      <c r="E2"/>
-      <c r="F2"/>
-      <c r="G2"/>
-      <c r="H2"/>
-      <c r="I2"/>
-      <c r="J2"/>
-    </row>
-    <row r="3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1169,17 +1177,17 @@
       <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="n">
-        <v>9467.104435</v>
+      <c r="H3">
+        <v>9467.1044349999993</v>
       </c>
       <c r="I3" t="s">
         <v>18</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>115</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1201,17 +1209,17 @@
       <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" t="n">
-        <v>4420.057664</v>
+      <c r="H4">
+        <v>4420.0576639999999</v>
       </c>
       <c r="I4" t="s">
         <v>18</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>62</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1233,17 +1241,17 @@
       <c r="G5" t="s">
         <v>17</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>2711.683982</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>41</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1265,17 +1273,17 @@
       <c r="G6" t="s">
         <v>17</v>
       </c>
-      <c r="H6" t="n">
-        <v>5169.666489</v>
+      <c r="H6">
+        <v>5169.6664890000002</v>
       </c>
       <c r="I6" t="s">
         <v>18</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>76</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1297,17 +1305,17 @@
       <c r="G7" t="s">
         <v>17</v>
       </c>
-      <c r="H7" t="n">
-        <v>718.953896</v>
+      <c r="H7">
+        <v>718.95389599999999</v>
       </c>
       <c r="I7" t="s">
         <v>18</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>19</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1329,17 +1337,17 @@
       <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="H8" t="n">
-        <v>49347.89057</v>
+      <c r="H8">
+        <v>49347.890570000003</v>
       </c>
       <c r="I8" t="s">
         <v>18</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>427</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -1361,17 +1369,17 @@
       <c r="G9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" t="n">
-        <v>10205.53698</v>
+      <c r="H9">
+        <v>10205.536980000001</v>
       </c>
       <c r="I9" t="s">
         <v>18</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1393,17 +1401,17 @@
       <c r="G10" t="s">
         <v>17</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>15139.5437</v>
       </c>
       <c r="I10" t="s">
         <v>18</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>132</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -1425,17 +1433,17 @@
       <c r="G11" t="s">
         <v>17</v>
       </c>
-      <c r="H11" t="n">
-        <v>414.480194</v>
+      <c r="H11">
+        <v>414.48019399999998</v>
       </c>
       <c r="I11" t="s">
         <v>18</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>8</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1457,17 +1465,17 @@
       <c r="G12" t="s">
         <v>17</v>
       </c>
-      <c r="H12" t="n">
-        <v>2073.67826</v>
+      <c r="H12">
+        <v>2073.6782600000001</v>
       </c>
       <c r="I12" t="s">
         <v>18</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>29</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1489,17 +1497,17 @@
       <c r="G13" t="s">
         <v>17</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>1148.442233</v>
       </c>
       <c r="I13" t="s">
         <v>18</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>18</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1521,17 +1529,17 @@
       <c r="G14" t="s">
         <v>17</v>
       </c>
-      <c r="H14" t="n">
-        <v>15682.55108</v>
+      <c r="H14">
+        <v>15682.551079999999</v>
       </c>
       <c r="I14" t="s">
         <v>18</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>161</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1553,17 +1561,17 @@
       <c r="G15" t="s">
         <v>17</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>6384.687398</v>
       </c>
       <c r="I15" t="s">
         <v>18</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>89</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -1585,17 +1593,17 @@
       <c r="G16" t="s">
         <v>17</v>
       </c>
-      <c r="H16" t="n">
-        <v>21898.79602</v>
+      <c r="H16">
+        <v>21898.796020000002</v>
       </c>
       <c r="I16" t="s">
         <v>18</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>178</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -1617,17 +1625,17 @@
       <c r="G17" t="s">
         <v>17</v>
       </c>
-      <c r="H17" t="n">
-        <v>18878.00817</v>
+      <c r="H17">
+        <v>18878.008170000001</v>
       </c>
       <c r="I17" t="s">
         <v>18</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>224</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -1649,17 +1657,17 @@
       <c r="G18" t="s">
         <v>17</v>
       </c>
-      <c r="H18" t="n">
-        <v>858.178368</v>
+      <c r="H18">
+        <v>858.17836799999998</v>
       </c>
       <c r="I18" t="s">
         <v>18</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>12</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1681,17 +1689,17 @@
       <c r="G19" t="s">
         <v>17</v>
       </c>
-      <c r="H19" t="n">
-        <v>35354.71351</v>
+      <c r="H19">
+        <v>35354.713510000001</v>
       </c>
       <c r="I19" t="s">
         <v>18</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>354</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1713,17 +1721,17 @@
       <c r="G20" t="s">
         <v>17</v>
       </c>
-      <c r="H20" t="n">
-        <v>2730.843313</v>
+      <c r="H20">
+        <v>2730.8433129999999</v>
       </c>
       <c r="I20" t="s">
         <v>18</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>35</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>50</v>
       </c>
@@ -1745,17 +1753,17 @@
       <c r="G21" t="s">
         <v>17</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>418.152399</v>
       </c>
       <c r="I21" t="s">
         <v>18</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>11</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>51</v>
       </c>
@@ -1777,17 +1785,17 @@
       <c r="G22" t="s">
         <v>17</v>
       </c>
-      <c r="H22" t="n">
-        <v>305.59133</v>
+      <c r="H22">
+        <v>305.59133000000003</v>
       </c>
       <c r="I22" t="s">
         <v>18</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>5</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1809,17 +1817,17 @@
       <c r="G23" t="s">
         <v>17</v>
       </c>
-      <c r="H23" t="n">
-        <v>29389.77512</v>
+      <c r="H23">
+        <v>29389.775119999998</v>
       </c>
       <c r="I23" t="s">
         <v>18</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>309</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -1841,17 +1849,17 @@
       <c r="G24" t="s">
         <v>17</v>
       </c>
-      <c r="H24" t="n">
-        <v>4404.88986</v>
+      <c r="H24">
+        <v>4404.8898600000002</v>
       </c>
       <c r="I24" t="s">
         <v>18</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>22</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -1873,17 +1881,17 @@
       <c r="G25" t="s">
         <v>17</v>
       </c>
-      <c r="H25" t="n">
-        <v>506.125661</v>
+      <c r="H25">
+        <v>506.12566099999998</v>
       </c>
       <c r="I25" t="s">
         <v>18</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>11</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -1905,17 +1913,17 @@
       <c r="G26" t="s">
         <v>17</v>
       </c>
-      <c r="H26" t="n">
-        <v>27141.90661</v>
+      <c r="H26">
+        <v>27141.906609999998</v>
       </c>
       <c r="I26" t="s">
         <v>18</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>256</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -1937,17 +1945,17 @@
       <c r="G27" t="s">
         <v>17</v>
       </c>
-      <c r="H27" t="n">
-        <v>10545.93443</v>
+      <c r="H27">
+        <v>10545.934429999999</v>
       </c>
       <c r="I27" t="s">
         <v>18</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>48</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -1969,17 +1977,17 @@
       <c r="G28" t="s">
         <v>17</v>
       </c>
-      <c r="H28" t="n">
-        <v>56693.89741</v>
+      <c r="H28">
+        <v>56693.897409999998</v>
       </c>
       <c r="I28" t="s">
         <v>18</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>509</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>61</v>
       </c>
@@ -2001,17 +2009,17 @@
       <c r="G29" t="s">
         <v>17</v>
       </c>
-      <c r="H29" t="n">
-        <v>6421.090127</v>
+      <c r="H29">
+        <v>6421.0901270000004</v>
       </c>
       <c r="I29" t="s">
         <v>18</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>51</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -2033,17 +2041,17 @@
       <c r="G30" t="s">
         <v>17</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>20465.83772</v>
       </c>
       <c r="I30" t="s">
         <v>18</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>229</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>64</v>
       </c>
@@ -2063,21 +2071,21 @@
         <v>24</v>
       </c>
       <c r="G31" t="s">
+        <v>252</v>
+      </c>
+      <c r="H31">
+        <v>77334.40436</v>
+      </c>
+      <c r="I31" t="s">
         <v>66</v>
       </c>
-      <c r="H31" t="n">
-        <v>77334.40436</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="J31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>67</v>
-      </c>
-      <c r="J31" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>68</v>
       </c>
       <c r="B32" t="s">
         <v>65</v>
@@ -2095,21 +2103,21 @@
         <v>24</v>
       </c>
       <c r="G32" t="s">
+        <v>252</v>
+      </c>
+      <c r="H32">
+        <v>82914.2402</v>
+      </c>
+      <c r="I32" t="s">
         <v>66</v>
       </c>
-      <c r="H32" t="n">
-        <v>82914.2402</v>
-      </c>
-      <c r="I32" t="s">
-        <v>67</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>109</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
         <v>65</v>
@@ -2127,21 +2135,21 @@
         <v>24</v>
       </c>
       <c r="G33" t="s">
+        <v>252</v>
+      </c>
+      <c r="H33">
+        <v>6908.3757779999996</v>
+      </c>
+      <c r="I33" t="s">
         <v>66</v>
       </c>
-      <c r="H33" t="n">
-        <v>6908.375778</v>
-      </c>
-      <c r="I33" t="s">
-        <v>67</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>96</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B34" t="s">
         <v>65</v>
@@ -2159,21 +2167,21 @@
         <v>24</v>
       </c>
       <c r="G34" t="s">
+        <v>252</v>
+      </c>
+      <c r="H34">
+        <v>806.12885200000005</v>
+      </c>
+      <c r="I34" t="s">
         <v>66</v>
       </c>
-      <c r="H34" t="n">
-        <v>806.128852</v>
-      </c>
-      <c r="I34" t="s">
-        <v>67</v>
-      </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>206</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
         <v>65</v>
@@ -2191,21 +2199,21 @@
         <v>16</v>
       </c>
       <c r="G35" t="s">
+        <v>252</v>
+      </c>
+      <c r="H35">
+        <v>595.37621100000001</v>
+      </c>
+      <c r="I35" t="s">
         <v>66</v>
       </c>
-      <c r="H35" t="n">
-        <v>595.376211</v>
-      </c>
-      <c r="I35" t="s">
-        <v>67</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>81</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
         <v>65</v>
@@ -2223,21 +2231,21 @@
         <v>16</v>
       </c>
       <c r="G36" t="s">
+        <v>252</v>
+      </c>
+      <c r="H36">
+        <v>58988.865940000003</v>
+      </c>
+      <c r="I36" t="s">
         <v>66</v>
       </c>
-      <c r="H36" t="n">
-        <v>58988.86594</v>
-      </c>
-      <c r="I36" t="s">
-        <v>67</v>
-      </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>192</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
         <v>65</v>
@@ -2255,21 +2263,21 @@
         <v>24</v>
       </c>
       <c r="G37" t="s">
+        <v>252</v>
+      </c>
+      <c r="H37">
+        <v>4421.8139359999996</v>
+      </c>
+      <c r="I37" t="s">
         <v>66</v>
       </c>
-      <c r="H37" t="n">
-        <v>4421.813936</v>
-      </c>
-      <c r="I37" t="s">
-        <v>67</v>
-      </c>
-      <c r="J37" t="n">
+      <c r="J37">
         <v>136</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
         <v>65</v>
@@ -2287,21 +2295,21 @@
         <v>24</v>
       </c>
       <c r="G38" t="s">
+        <v>252</v>
+      </c>
+      <c r="H38">
+        <v>23058.095209999999</v>
+      </c>
+      <c r="I38" t="s">
         <v>66</v>
       </c>
-      <c r="H38" t="n">
-        <v>23058.09521</v>
-      </c>
-      <c r="I38" t="s">
-        <v>67</v>
-      </c>
-      <c r="J38" t="n">
+      <c r="J38">
         <v>155</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B39" t="s">
         <v>65</v>
@@ -2319,21 +2327,21 @@
         <v>24</v>
       </c>
       <c r="G39" t="s">
+        <v>252</v>
+      </c>
+      <c r="H39">
+        <v>1137.265956</v>
+      </c>
+      <c r="I39" t="s">
         <v>66</v>
       </c>
-      <c r="H39" t="n">
-        <v>1137.265956</v>
-      </c>
-      <c r="I39" t="s">
-        <v>67</v>
-      </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>65</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" t="s">
         <v>65</v>
@@ -2351,21 +2359,21 @@
         <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>66</v>
-      </c>
-      <c r="H40" t="n">
-        <v>2665.701588</v>
+        <v>252</v>
+      </c>
+      <c r="H40">
+        <v>2665.7015879999999</v>
       </c>
       <c r="I40" t="s">
+        <v>76</v>
+      </c>
+      <c r="J40">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>77</v>
-      </c>
-      <c r="J40" t="n">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>78</v>
       </c>
       <c r="B41" t="s">
         <v>65</v>
@@ -2383,21 +2391,21 @@
         <v>24</v>
       </c>
       <c r="G41" t="s">
-        <v>66</v>
-      </c>
-      <c r="H41" t="n">
-        <v>60655.24875</v>
+        <v>252</v>
+      </c>
+      <c r="H41">
+        <v>60655.248749999999</v>
       </c>
       <c r="I41" t="s">
-        <v>77</v>
-      </c>
-      <c r="J41" t="n">
+        <v>76</v>
+      </c>
+      <c r="J41">
         <v>155</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
         <v>65</v>
@@ -2415,21 +2423,21 @@
         <v>24</v>
       </c>
       <c r="G42" t="s">
-        <v>66</v>
-      </c>
-      <c r="H42" t="n">
+        <v>252</v>
+      </c>
+      <c r="H42">
         <v>14165.93037</v>
       </c>
       <c r="I42" t="s">
-        <v>77</v>
-      </c>
-      <c r="J42" t="n">
+        <v>76</v>
+      </c>
+      <c r="J42">
         <v>98</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B43" t="s">
         <v>65</v>
@@ -2447,21 +2455,21 @@
         <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>66</v>
-      </c>
-      <c r="H43" t="n">
-        <v>3694.876985</v>
+        <v>252</v>
+      </c>
+      <c r="H43">
+        <v>3694.8769849999999</v>
       </c>
       <c r="I43" t="s">
-        <v>77</v>
-      </c>
-      <c r="J43" t="n">
+        <v>76</v>
+      </c>
+      <c r="J43">
         <v>129</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B44" t="s">
         <v>65</v>
@@ -2479,21 +2487,21 @@
         <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>66</v>
-      </c>
-      <c r="H44" t="n">
+        <v>252</v>
+      </c>
+      <c r="H44">
         <v>144972.9099</v>
       </c>
       <c r="I44" t="s">
-        <v>77</v>
-      </c>
-      <c r="J44" t="n">
+        <v>76</v>
+      </c>
+      <c r="J44">
         <v>193</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
         <v>65</v>
@@ -2511,21 +2519,21 @@
         <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
-      </c>
-      <c r="H45" t="n">
+        <v>252</v>
+      </c>
+      <c r="H45">
         <v>6211.455113</v>
       </c>
       <c r="I45" t="s">
-        <v>77</v>
-      </c>
-      <c r="J45" t="n">
+        <v>76</v>
+      </c>
+      <c r="J45">
         <v>118</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B46" t="s">
         <v>65</v>
@@ -2543,21 +2551,21 @@
         <v>24</v>
       </c>
       <c r="G46" t="s">
+        <v>252</v>
+      </c>
+      <c r="H46">
+        <v>81969.525519999996</v>
+      </c>
+      <c r="I46" t="s">
         <v>66</v>
       </c>
-      <c r="H46" t="n">
-        <v>81969.52552</v>
-      </c>
-      <c r="I46" t="s">
-        <v>67</v>
-      </c>
-      <c r="J46" t="n">
+      <c r="J46">
         <v>96</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B47" t="s">
         <v>65</v>
@@ -2575,21 +2583,21 @@
         <v>24</v>
       </c>
       <c r="G47" t="s">
+        <v>252</v>
+      </c>
+      <c r="H47">
+        <v>22798.166949999999</v>
+      </c>
+      <c r="I47" t="s">
         <v>66</v>
       </c>
-      <c r="H47" t="n">
-        <v>22798.16695</v>
-      </c>
-      <c r="I47" t="s">
-        <v>67</v>
-      </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>130</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48" t="s">
         <v>65</v>
@@ -2607,21 +2615,21 @@
         <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" t="n">
+        <v>252</v>
+      </c>
+      <c r="H48">
         <v>233948.5238</v>
       </c>
       <c r="I48" t="s">
-        <v>77</v>
-      </c>
-      <c r="J48" t="n">
+        <v>76</v>
+      </c>
+      <c r="J48">
         <v>246</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B49" t="s">
         <v>65</v>
@@ -2639,24 +2647,24 @@
         <v>24</v>
       </c>
       <c r="G49" t="s">
-        <v>66</v>
-      </c>
-      <c r="H49" t="n">
+        <v>252</v>
+      </c>
+      <c r="H49">
         <v>10648.43685</v>
       </c>
       <c r="I49" t="s">
-        <v>77</v>
-      </c>
-      <c r="J49" t="n">
+        <v>76</v>
+      </c>
+      <c r="J49">
         <v>43</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" t="s">
         <v>87</v>
-      </c>
-      <c r="B50" t="s">
-        <v>88</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
@@ -2665,30 +2673,30 @@
         <v>41</v>
       </c>
       <c r="E50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F50" t="s">
         <v>16</v>
       </c>
       <c r="G50" t="s">
+        <v>88</v>
+      </c>
+      <c r="H50">
+        <v>18928.78039</v>
+      </c>
+      <c r="I50" t="s">
         <v>89</v>
       </c>
-      <c r="H50" t="n">
-        <v>18928.78039</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="J50">
         <v>90</v>
       </c>
-      <c r="J50" t="n">
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>91</v>
-      </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
         <v>22</v>
@@ -2697,30 +2705,30 @@
         <v>15</v>
       </c>
       <c r="E51" t="s">
+        <v>87</v>
+      </c>
+      <c r="F51" t="s">
+        <v>24</v>
+      </c>
+      <c r="G51" t="s">
         <v>88</v>
       </c>
-      <c r="F51" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" t="s">
-        <v>89</v>
-      </c>
-      <c r="H51" t="n">
-        <v>7810.93993</v>
+      <c r="H51">
+        <v>7810.9399299999995</v>
       </c>
       <c r="I51" t="s">
+        <v>91</v>
+      </c>
+      <c r="J51">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>92</v>
       </c>
-      <c r="J51" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>93</v>
-      </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
         <v>26</v>
@@ -2729,30 +2737,30 @@
         <v>15</v>
       </c>
       <c r="E52" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" t="s">
+        <v>24</v>
+      </c>
+      <c r="G52" t="s">
         <v>88</v>
       </c>
-      <c r="F52" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" t="s">
-        <v>89</v>
-      </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>12702.15748</v>
       </c>
       <c r="I52" t="s">
-        <v>92</v>
-      </c>
-      <c r="J52" t="n">
+        <v>91</v>
+      </c>
+      <c r="J52">
         <v>239</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C53" t="s">
         <v>26</v>
@@ -2761,30 +2769,30 @@
         <v>41</v>
       </c>
       <c r="E53" t="s">
+        <v>87</v>
+      </c>
+      <c r="F53" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
         <v>88</v>
       </c>
-      <c r="F53" t="s">
-        <v>24</v>
-      </c>
-      <c r="G53" t="s">
+      <c r="H53">
+        <v>11771.65263</v>
+      </c>
+      <c r="I53" t="s">
         <v>89</v>
       </c>
-      <c r="H53" t="n">
-        <v>11771.65263</v>
-      </c>
-      <c r="I53" t="s">
-        <v>90</v>
-      </c>
-      <c r="J53" t="n">
+      <c r="J53">
         <v>79</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
@@ -2793,30 +2801,30 @@
         <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F54" t="s">
         <v>16</v>
       </c>
       <c r="G54" t="s">
-        <v>89</v>
-      </c>
-      <c r="H54" t="n">
-        <v>6415.182666</v>
+        <v>88</v>
+      </c>
+      <c r="H54">
+        <v>6415.1826659999997</v>
       </c>
       <c r="I54" t="s">
-        <v>92</v>
-      </c>
-      <c r="J54" t="n">
+        <v>91</v>
+      </c>
+      <c r="J54">
         <v>278</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C55" t="s">
         <v>22</v>
@@ -2825,30 +2833,30 @@
         <v>23</v>
       </c>
       <c r="E55" t="s">
+        <v>87</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" t="s">
         <v>88</v>
       </c>
-      <c r="F55" t="s">
-        <v>24</v>
-      </c>
-      <c r="G55" t="s">
-        <v>89</v>
-      </c>
-      <c r="H55" t="n">
-        <v>25655.62151</v>
+      <c r="H55">
+        <v>25655.621510000001</v>
       </c>
       <c r="I55" t="s">
-        <v>92</v>
-      </c>
-      <c r="J55" t="n">
+        <v>91</v>
+      </c>
+      <c r="J55">
         <v>35</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C56" t="s">
         <v>22</v>
@@ -2857,30 +2865,30 @@
         <v>44</v>
       </c>
       <c r="E56" t="s">
+        <v>87</v>
+      </c>
+      <c r="F56" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" t="s">
         <v>88</v>
       </c>
-      <c r="F56" t="s">
-        <v>24</v>
-      </c>
-      <c r="G56" t="s">
+      <c r="H56">
+        <v>21003.735939999999</v>
+      </c>
+      <c r="I56" t="s">
         <v>89</v>
       </c>
-      <c r="H56" t="n">
-        <v>21003.73594</v>
-      </c>
-      <c r="I56" t="s">
-        <v>90</v>
-      </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>44</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C57" t="s">
         <v>26</v>
@@ -2889,30 +2897,30 @@
         <v>23</v>
       </c>
       <c r="E57" t="s">
+        <v>87</v>
+      </c>
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" t="s">
         <v>88</v>
       </c>
-      <c r="F57" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" t="s">
-        <v>89</v>
-      </c>
-      <c r="H57" t="n">
-        <v>19759.17773</v>
+      <c r="H57">
+        <v>19759.177729999999</v>
       </c>
       <c r="I57" t="s">
-        <v>92</v>
-      </c>
-      <c r="J57" t="n">
+        <v>91</v>
+      </c>
+      <c r="J57">
         <v>347</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C58" t="s">
         <v>14</v>
@@ -2921,30 +2929,30 @@
         <v>44</v>
       </c>
       <c r="E58" t="s">
+        <v>87</v>
+      </c>
+      <c r="F58" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" t="s">
         <v>88</v>
       </c>
-      <c r="F58" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="H58">
+        <v>3343.303261</v>
+      </c>
+      <c r="I58" t="s">
         <v>89</v>
       </c>
-      <c r="H58" t="n">
-        <v>3343.303261</v>
-      </c>
-      <c r="I58" t="s">
-        <v>90</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="J58">
         <v>72</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C59" t="s">
         <v>22</v>
@@ -2953,30 +2961,30 @@
         <v>28</v>
       </c>
       <c r="E59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F59" t="s">
         <v>16</v>
       </c>
       <c r="G59" t="s">
-        <v>89</v>
-      </c>
-      <c r="H59" t="n">
-        <v>23874.12305</v>
+        <v>88</v>
+      </c>
+      <c r="H59">
+        <v>23874.123049999998</v>
       </c>
       <c r="I59" t="s">
-        <v>92</v>
-      </c>
-      <c r="J59" t="n">
+        <v>91</v>
+      </c>
+      <c r="J59">
         <v>137</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
@@ -2985,30 +2993,30 @@
         <v>35</v>
       </c>
       <c r="E60" t="s">
+        <v>87</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" t="s">
         <v>88</v>
       </c>
-      <c r="F60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" t="s">
-        <v>89</v>
-      </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>12355.21392</v>
       </c>
       <c r="I60" t="s">
-        <v>92</v>
-      </c>
-      <c r="J60" t="n">
+        <v>91</v>
+      </c>
+      <c r="J60">
         <v>19</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B61" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C61" t="s">
         <v>26</v>
@@ -3017,30 +3025,30 @@
         <v>44</v>
       </c>
       <c r="E61" t="s">
+        <v>87</v>
+      </c>
+      <c r="F61" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" t="s">
         <v>88</v>
       </c>
-      <c r="F61" t="s">
-        <v>24</v>
-      </c>
-      <c r="G61" t="s">
+      <c r="H61">
+        <v>13656.292160000001</v>
+      </c>
+      <c r="I61" t="s">
         <v>89</v>
       </c>
-      <c r="H61" t="n">
-        <v>13656.29216</v>
-      </c>
-      <c r="I61" t="s">
-        <v>90</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="J61">
         <v>275</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C62" t="s">
         <v>26</v>
@@ -3049,30 +3057,30 @@
         <v>35</v>
       </c>
       <c r="E62" t="s">
+        <v>87</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" t="s">
         <v>88</v>
       </c>
-      <c r="F62" t="s">
-        <v>24</v>
-      </c>
-      <c r="G62" t="s">
-        <v>89</v>
-      </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>9381.047106</v>
       </c>
       <c r="I62" t="s">
-        <v>92</v>
-      </c>
-      <c r="J62" t="n">
+        <v>91</v>
+      </c>
+      <c r="J62">
         <v>41</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
@@ -3081,30 +3089,30 @@
         <v>46</v>
       </c>
       <c r="E63" t="s">
+        <v>87</v>
+      </c>
+      <c r="F63" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" t="s">
         <v>88</v>
       </c>
-      <c r="F63" t="s">
-        <v>24</v>
-      </c>
-      <c r="G63" t="s">
-        <v>89</v>
-      </c>
-      <c r="H63" t="n">
-        <v>31776.54878</v>
+      <c r="H63">
+        <v>31776.548780000001</v>
       </c>
       <c r="I63" t="s">
-        <v>92</v>
-      </c>
-      <c r="J63" t="n">
+        <v>91</v>
+      </c>
+      <c r="J63">
         <v>27</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B64" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -3113,30 +3121,30 @@
         <v>38</v>
       </c>
       <c r="E64" t="s">
+        <v>87</v>
+      </c>
+      <c r="F64" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" t="s">
         <v>88</v>
       </c>
-      <c r="F64" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" t="s">
+      <c r="H64">
+        <v>6332.9572040000003</v>
+      </c>
+      <c r="I64" t="s">
         <v>89</v>
       </c>
-      <c r="H64" t="n">
-        <v>6332.957204</v>
-      </c>
-      <c r="I64" t="s">
-        <v>90</v>
-      </c>
-      <c r="J64" t="n">
+      <c r="J64">
         <v>64</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C65" t="s">
         <v>26</v>
@@ -3145,30 +3153,30 @@
         <v>46</v>
       </c>
       <c r="E65" t="s">
+        <v>87</v>
+      </c>
+      <c r="F65" t="s">
+        <v>24</v>
+      </c>
+      <c r="G65" t="s">
         <v>88</v>
       </c>
-      <c r="F65" t="s">
-        <v>24</v>
-      </c>
-      <c r="G65" t="s">
-        <v>89</v>
-      </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>12090.81516</v>
       </c>
       <c r="I65" t="s">
-        <v>92</v>
-      </c>
-      <c r="J65" t="n">
+        <v>91</v>
+      </c>
+      <c r="J65">
         <v>158</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C66" t="s">
         <v>22</v>
@@ -3177,30 +3185,30 @@
         <v>32</v>
       </c>
       <c r="E66" t="s">
+        <v>87</v>
+      </c>
+      <c r="F66" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" t="s">
         <v>88</v>
       </c>
-      <c r="F66" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" t="s">
-        <v>89</v>
-      </c>
-      <c r="H66" t="n">
-        <v>7067.238565</v>
+      <c r="H66">
+        <v>7067.2385649999997</v>
       </c>
       <c r="I66" t="s">
-        <v>92</v>
-      </c>
-      <c r="J66" t="n">
+        <v>91</v>
+      </c>
+      <c r="J66">
         <v>72</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C67" t="s">
         <v>26</v>
@@ -3209,30 +3217,30 @@
         <v>38</v>
       </c>
       <c r="E67" t="s">
+        <v>87</v>
+      </c>
+      <c r="F67" t="s">
+        <v>24</v>
+      </c>
+      <c r="G67" t="s">
         <v>88</v>
       </c>
-      <c r="F67" t="s">
-        <v>24</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="H67">
+        <v>28805.255870000001</v>
+      </c>
+      <c r="I67" t="s">
         <v>89</v>
       </c>
-      <c r="H67" t="n">
-        <v>28805.25587</v>
-      </c>
-      <c r="I67" t="s">
-        <v>90</v>
-      </c>
-      <c r="J67" t="n">
+      <c r="J67">
         <v>80</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C68" t="s">
         <v>22</v>
@@ -3241,30 +3249,30 @@
         <v>49</v>
       </c>
       <c r="E68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F68" t="s">
         <v>16</v>
       </c>
       <c r="G68" t="s">
-        <v>89</v>
-      </c>
-      <c r="H68" t="n">
-        <v>3206.154383</v>
+        <v>88</v>
+      </c>
+      <c r="H68">
+        <v>3206.1543830000001</v>
       </c>
       <c r="I68" t="s">
-        <v>92</v>
-      </c>
-      <c r="J68" t="n">
+        <v>91</v>
+      </c>
+      <c r="J68">
         <v>44</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
         <v>26</v>
@@ -3273,30 +3281,30 @@
         <v>32</v>
       </c>
       <c r="E69" t="s">
+        <v>87</v>
+      </c>
+      <c r="F69" t="s">
+        <v>24</v>
+      </c>
+      <c r="G69" t="s">
         <v>88</v>
       </c>
-      <c r="F69" t="s">
-        <v>24</v>
-      </c>
-      <c r="G69" t="s">
-        <v>89</v>
-      </c>
-      <c r="H69" t="n">
+      <c r="H69">
         <v>19224.79206</v>
       </c>
       <c r="I69" t="s">
-        <v>92</v>
-      </c>
-      <c r="J69" t="n">
+        <v>91</v>
+      </c>
+      <c r="J69">
         <v>303</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C70" t="s">
         <v>22</v>
@@ -3305,30 +3313,30 @@
         <v>35</v>
       </c>
       <c r="E70" t="s">
+        <v>87</v>
+      </c>
+      <c r="F70" t="s">
+        <v>24</v>
+      </c>
+      <c r="G70" t="s">
         <v>88</v>
       </c>
-      <c r="F70" t="s">
-        <v>24</v>
-      </c>
-      <c r="G70" t="s">
-        <v>89</v>
-      </c>
-      <c r="H70" t="n">
-        <v>1153.072405</v>
+      <c r="H70">
+        <v>1153.0724049999999</v>
       </c>
       <c r="I70" t="s">
-        <v>92</v>
-      </c>
-      <c r="J70" t="n">
+        <v>91</v>
+      </c>
+      <c r="J70">
         <v>30</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>111</v>
+      </c>
+      <c r="B71" t="s">
         <v>112</v>
-      </c>
-      <c r="B71" t="s">
-        <v>113</v>
       </c>
       <c r="C71" t="s">
         <v>26</v>
@@ -3337,30 +3345,30 @@
         <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F71" t="s">
         <v>29</v>
       </c>
       <c r="G71" t="s">
+        <v>113</v>
+      </c>
+      <c r="H71">
+        <v>13757.35763</v>
+      </c>
+      <c r="I71" t="s">
         <v>114</v>
       </c>
-      <c r="H71" t="n">
-        <v>13757.35763</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="J71">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>115</v>
       </c>
-      <c r="J71" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>116</v>
-      </c>
       <c r="B72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
         <v>22</v>
@@ -3369,30 +3377,30 @@
         <v>15</v>
       </c>
       <c r="E72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F72" t="s">
         <v>29</v>
       </c>
       <c r="G72" t="s">
+        <v>113</v>
+      </c>
+      <c r="H72">
+        <v>27630.469550000002</v>
+      </c>
+      <c r="I72" t="s">
         <v>114</v>
       </c>
-      <c r="H72" t="n">
-        <v>27630.46955</v>
-      </c>
-      <c r="I72" t="s">
-        <v>115</v>
-      </c>
-      <c r="J72" t="n">
+      <c r="J72">
         <v>39</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C73" t="s">
         <v>22</v>
@@ -3401,30 +3409,30 @@
         <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F73" t="s">
         <v>16</v>
       </c>
       <c r="G73" t="s">
+        <v>113</v>
+      </c>
+      <c r="H73">
+        <v>2455.4279299999998</v>
+      </c>
+      <c r="I73" t="s">
         <v>114</v>
       </c>
-      <c r="H73" t="n">
-        <v>2455.42793</v>
-      </c>
-      <c r="I73" t="s">
-        <v>115</v>
-      </c>
-      <c r="J73" t="n">
+      <c r="J73">
         <v>16</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -3433,30 +3441,30 @@
         <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F74" t="s">
         <v>16</v>
       </c>
       <c r="G74" t="s">
+        <v>113</v>
+      </c>
+      <c r="H74">
+        <v>9023.0869390000007</v>
+      </c>
+      <c r="I74" t="s">
         <v>114</v>
       </c>
-      <c r="H74" t="n">
-        <v>9023.086939</v>
-      </c>
-      <c r="I74" t="s">
-        <v>115</v>
-      </c>
-      <c r="J74" t="n">
+      <c r="J74">
         <v>43</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B75" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C75" t="s">
         <v>22</v>
@@ -3465,30 +3473,30 @@
         <v>23</v>
       </c>
       <c r="E75" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F75" t="s">
         <v>16</v>
       </c>
       <c r="G75" t="s">
+        <v>113</v>
+      </c>
+      <c r="H75">
+        <v>26462.867989999999</v>
+      </c>
+      <c r="I75" t="s">
         <v>114</v>
       </c>
-      <c r="H75" t="n">
-        <v>26462.86799</v>
-      </c>
-      <c r="I75" t="s">
-        <v>115</v>
-      </c>
-      <c r="J75" t="n">
+      <c r="J75">
         <v>34</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B76" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -3497,30 +3505,30 @@
         <v>23</v>
       </c>
       <c r="E76" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F76" t="s">
         <v>16</v>
       </c>
       <c r="G76" t="s">
+        <v>113</v>
+      </c>
+      <c r="H76">
+        <v>4583.7102830000003</v>
+      </c>
+      <c r="I76" t="s">
         <v>114</v>
       </c>
-      <c r="H76" t="n">
-        <v>4583.710283</v>
-      </c>
-      <c r="I76" t="s">
-        <v>115</v>
-      </c>
-      <c r="J76" t="n">
+      <c r="J76">
         <v>5</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C77" t="s">
         <v>22</v>
@@ -3529,30 +3537,30 @@
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F77" t="s">
         <v>16</v>
       </c>
       <c r="G77" t="s">
+        <v>113</v>
+      </c>
+      <c r="H77">
+        <v>13002.47999</v>
+      </c>
+      <c r="I77" t="s">
         <v>114</v>
       </c>
-      <c r="H77" t="n">
-        <v>13002.47999</v>
-      </c>
-      <c r="I77" t="s">
-        <v>115</v>
-      </c>
-      <c r="J77" t="n">
+      <c r="J77">
         <v>7</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B78" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -3561,30 +3569,30 @@
         <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
       </c>
       <c r="G78" t="s">
+        <v>113</v>
+      </c>
+      <c r="H78">
+        <v>2115.509466</v>
+      </c>
+      <c r="I78" t="s">
         <v>114</v>
       </c>
-      <c r="H78" t="n">
-        <v>2115.509466</v>
-      </c>
-      <c r="I78" t="s">
-        <v>115</v>
-      </c>
-      <c r="J78" t="n">
+      <c r="J78">
         <v>31</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C79" t="s">
         <v>26</v>
@@ -3593,30 +3601,30 @@
         <v>32</v>
       </c>
       <c r="E79" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F79" t="s">
         <v>29</v>
       </c>
       <c r="G79" t="s">
+        <v>113</v>
+      </c>
+      <c r="H79">
+        <v>1173.6686850000001</v>
+      </c>
+      <c r="I79" t="s">
         <v>114</v>
       </c>
-      <c r="H79" t="n">
-        <v>1173.668685</v>
-      </c>
-      <c r="I79" t="s">
-        <v>115</v>
-      </c>
-      <c r="J79" t="n">
+      <c r="J79">
         <v>236</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C80" t="s">
         <v>26</v>
@@ -3625,30 +3633,30 @@
         <v>35</v>
       </c>
       <c r="E80" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F80" t="s">
         <v>29</v>
       </c>
       <c r="G80" t="s">
+        <v>113</v>
+      </c>
+      <c r="H80">
+        <v>8124.8336360000003</v>
+      </c>
+      <c r="I80" t="s">
         <v>114</v>
       </c>
-      <c r="H80" t="n">
-        <v>8124.833636</v>
-      </c>
-      <c r="I80" t="s">
-        <v>115</v>
-      </c>
-      <c r="J80" t="n">
+      <c r="J80">
         <v>481</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C81" t="s">
         <v>22</v>
@@ -3657,30 +3665,30 @@
         <v>35</v>
       </c>
       <c r="E81" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F81" t="s">
         <v>29</v>
       </c>
       <c r="G81" t="s">
+        <v>113</v>
+      </c>
+      <c r="H81">
+        <v>6629.1285289999996</v>
+      </c>
+      <c r="I81" t="s">
         <v>114</v>
       </c>
-      <c r="H81" t="n">
-        <v>6629.128529</v>
-      </c>
-      <c r="I81" t="s">
-        <v>115</v>
-      </c>
-      <c r="J81" t="n">
+      <c r="J81">
         <v>81</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B82" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C82" t="s">
         <v>22</v>
@@ -3689,30 +3697,30 @@
         <v>38</v>
       </c>
       <c r="E82" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F82" t="s">
         <v>16</v>
       </c>
       <c r="G82" t="s">
+        <v>113</v>
+      </c>
+      <c r="H82">
+        <v>7694.3873329999997</v>
+      </c>
+      <c r="I82" t="s">
         <v>114</v>
       </c>
-      <c r="H82" t="n">
-        <v>7694.387333</v>
-      </c>
-      <c r="I82" t="s">
-        <v>115</v>
-      </c>
-      <c r="J82" t="n">
+      <c r="J82">
         <v>18</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -3721,30 +3729,30 @@
         <v>38</v>
       </c>
       <c r="E83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F83" t="s">
         <v>16</v>
       </c>
       <c r="G83" t="s">
+        <v>113</v>
+      </c>
+      <c r="H83">
+        <v>16211.18895</v>
+      </c>
+      <c r="I83" t="s">
         <v>114</v>
       </c>
-      <c r="H83" t="n">
-        <v>16211.18895</v>
-      </c>
-      <c r="I83" t="s">
-        <v>115</v>
-      </c>
-      <c r="J83" t="n">
+      <c r="J83">
         <v>4</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B84" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C84" t="s">
         <v>26</v>
@@ -3753,30 +3761,30 @@
         <v>41</v>
       </c>
       <c r="E84" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F84" t="s">
         <v>29</v>
       </c>
       <c r="G84" t="s">
+        <v>113</v>
+      </c>
+      <c r="H84">
+        <v>32189.11305</v>
+      </c>
+      <c r="I84" t="s">
         <v>114</v>
       </c>
-      <c r="H84" t="n">
-        <v>32189.11305</v>
-      </c>
-      <c r="I84" t="s">
-        <v>115</v>
-      </c>
-      <c r="J84" t="n">
+      <c r="J84">
         <v>183</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B85" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C85" t="s">
         <v>22</v>
@@ -3785,30 +3793,30 @@
         <v>44</v>
       </c>
       <c r="E85" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F85" t="s">
         <v>16</v>
       </c>
       <c r="G85" t="s">
+        <v>113</v>
+      </c>
+      <c r="H85">
+        <v>2311.0943029999999</v>
+      </c>
+      <c r="I85" t="s">
         <v>114</v>
       </c>
-      <c r="H85" t="n">
-        <v>2311.094303</v>
-      </c>
-      <c r="I85" t="s">
-        <v>115</v>
-      </c>
-      <c r="J85" t="n">
+      <c r="J85">
         <v>60</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B86" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C86" t="s">
         <v>26</v>
@@ -3817,30 +3825,30 @@
         <v>46</v>
       </c>
       <c r="E86" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F86" t="s">
         <v>29</v>
       </c>
       <c r="G86" t="s">
+        <v>113</v>
+      </c>
+      <c r="H86">
+        <v>3535.2158930000001</v>
+      </c>
+      <c r="I86" t="s">
         <v>114</v>
       </c>
-      <c r="H86" t="n">
-        <v>3535.215893</v>
-      </c>
-      <c r="I86" t="s">
-        <v>115</v>
-      </c>
-      <c r="J86" t="n">
+      <c r="J86">
         <v>77</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C87" t="s">
         <v>22</v>
@@ -3849,30 +3857,30 @@
         <v>49</v>
       </c>
       <c r="E87" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F87" t="s">
         <v>16</v>
       </c>
       <c r="G87" t="s">
+        <v>113</v>
+      </c>
+      <c r="H87">
+        <v>13830.322749999999</v>
+      </c>
+      <c r="I87" t="s">
         <v>114</v>
       </c>
-      <c r="H87" t="n">
-        <v>13830.32275</v>
-      </c>
-      <c r="I87" t="s">
-        <v>115</v>
-      </c>
-      <c r="J87" t="n">
+      <c r="J87">
         <v>18</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B88" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -3881,30 +3889,30 @@
         <v>49</v>
       </c>
       <c r="E88" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F88" t="s">
         <v>16</v>
       </c>
       <c r="G88" t="s">
+        <v>113</v>
+      </c>
+      <c r="H88">
+        <v>2330.4132949999998</v>
+      </c>
+      <c r="I88" t="s">
         <v>114</v>
       </c>
-      <c r="H88" t="n">
-        <v>2330.413295</v>
-      </c>
-      <c r="I88" t="s">
-        <v>115</v>
-      </c>
-      <c r="J88" t="n">
+      <c r="J88">
         <v>32</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C89" t="s">
         <v>26</v>
@@ -3913,30 +3921,30 @@
         <v>52</v>
       </c>
       <c r="E89" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F89" t="s">
         <v>29</v>
       </c>
       <c r="G89" t="s">
+        <v>113</v>
+      </c>
+      <c r="H89">
+        <v>2754.6328159999998</v>
+      </c>
+      <c r="I89" t="s">
         <v>114</v>
       </c>
-      <c r="H89" t="n">
-        <v>2754.632816</v>
-      </c>
-      <c r="I89" t="s">
-        <v>115</v>
-      </c>
-      <c r="J89" t="n">
+      <c r="J89">
         <v>287</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B90" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C90" t="s">
         <v>26</v>
@@ -3945,30 +3953,30 @@
         <v>55</v>
       </c>
       <c r="E90" t="s">
+        <v>112</v>
+      </c>
+      <c r="F90" t="s">
+        <v>24</v>
+      </c>
+      <c r="G90" t="s">
         <v>113</v>
       </c>
-      <c r="F90" t="s">
-        <v>24</v>
-      </c>
-      <c r="G90" t="s">
+      <c r="H90">
+        <v>75106.333830000003</v>
+      </c>
+      <c r="I90" t="s">
         <v>114</v>
       </c>
-      <c r="H90" t="n">
-        <v>75106.33383</v>
-      </c>
-      <c r="I90" t="s">
-        <v>115</v>
-      </c>
-      <c r="J90" t="n">
+      <c r="J90">
         <v>131</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B91" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C91" t="s">
         <v>22</v>
@@ -3977,30 +3985,30 @@
         <v>55</v>
       </c>
       <c r="E91" t="s">
+        <v>112</v>
+      </c>
+      <c r="F91" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" t="s">
         <v>113</v>
       </c>
-      <c r="F91" t="s">
-        <v>24</v>
-      </c>
-      <c r="G91" t="s">
+      <c r="H91">
+        <v>2577.5686649999998</v>
+      </c>
+      <c r="I91" t="s">
         <v>114</v>
       </c>
-      <c r="H91" t="n">
-        <v>2577.568665</v>
-      </c>
-      <c r="I91" t="s">
-        <v>115</v>
-      </c>
-      <c r="J91" t="n">
+      <c r="J91">
         <v>84</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C92" t="s">
         <v>26</v>
@@ -4009,30 +4017,30 @@
         <v>59</v>
       </c>
       <c r="E92" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F92" t="s">
         <v>29</v>
       </c>
       <c r="G92" t="s">
+        <v>113</v>
+      </c>
+      <c r="H92">
+        <v>719.91186300000004</v>
+      </c>
+      <c r="I92" t="s">
         <v>114</v>
       </c>
-      <c r="H92" t="n">
-        <v>719.911863</v>
-      </c>
-      <c r="I92" t="s">
-        <v>115</v>
-      </c>
-      <c r="J92" t="n">
+      <c r="J92">
         <v>1177</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C93" t="s">
         <v>22</v>
@@ -4041,30 +4049,30 @@
         <v>59</v>
       </c>
       <c r="E93" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F93" t="s">
         <v>29</v>
       </c>
       <c r="G93" t="s">
+        <v>113</v>
+      </c>
+      <c r="H93">
+        <v>3353.3619100000001</v>
+      </c>
+      <c r="I93" t="s">
         <v>114</v>
       </c>
-      <c r="H93" t="n">
-        <v>3353.36191</v>
-      </c>
-      <c r="I93" t="s">
-        <v>115</v>
-      </c>
-      <c r="J93" t="n">
+      <c r="J93">
         <v>105</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C94" t="s">
         <v>26</v>
@@ -4073,30 +4081,30 @@
         <v>62</v>
       </c>
       <c r="E94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F94" t="s">
         <v>29</v>
       </c>
       <c r="G94" t="s">
+        <v>113</v>
+      </c>
+      <c r="H94">
+        <v>2561.1235729999999</v>
+      </c>
+      <c r="I94" t="s">
         <v>114</v>
       </c>
-      <c r="H94" t="n">
-        <v>2561.123573</v>
-      </c>
-      <c r="I94" t="s">
-        <v>115</v>
-      </c>
-      <c r="J94" t="n">
+      <c r="J94">
         <v>607</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B95" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C95" t="s">
         <v>22</v>
@@ -4105,110 +4113,102 @@
         <v>62</v>
       </c>
       <c r="E95" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F95" t="s">
         <v>29</v>
       </c>
       <c r="G95" t="s">
+        <v>113</v>
+      </c>
+      <c r="H95">
+        <v>448.64766800000001</v>
+      </c>
+      <c r="I95" t="s">
         <v>114</v>
       </c>
-      <c r="H95" t="n">
-        <v>448.647668</v>
-      </c>
-      <c r="I95" t="s">
-        <v>115</v>
-      </c>
-      <c r="J95" t="n">
+      <c r="J95">
         <v>247</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
+        <v>139</v>
+      </c>
+      <c r="B96" t="s">
+        <v>112</v>
+      </c>
+      <c r="C96" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" t="s">
         <v>140</v>
       </c>
-      <c r="B96" t="s">
-        <v>113</v>
-      </c>
-      <c r="C96" t="s">
-        <v>26</v>
-      </c>
-      <c r="D96" t="s">
-        <v>141</v>
-      </c>
       <c r="E96" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F96" t="s">
         <v>29</v>
       </c>
       <c r="G96" t="s">
+        <v>113</v>
+      </c>
+      <c r="H96">
+        <v>319.80116700000002</v>
+      </c>
+      <c r="I96" t="s">
         <v>114</v>
       </c>
-      <c r="H96" t="n">
-        <v>319.801167</v>
-      </c>
-      <c r="I96" t="s">
-        <v>115</v>
-      </c>
-      <c r="J96" t="n">
+      <c r="J96">
         <v>1916</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B97" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C97" t="s">
         <v>22</v>
       </c>
       <c r="D97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E97" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F97" t="s">
         <v>29</v>
       </c>
       <c r="G97" t="s">
+        <v>113</v>
+      </c>
+      <c r="H97">
+        <v>3477.2589170000001</v>
+      </c>
+      <c r="I97" t="s">
         <v>114</v>
       </c>
-      <c r="H97" t="n">
-        <v>3477.258917</v>
-      </c>
-      <c r="I97" t="s">
-        <v>115</v>
-      </c>
-      <c r="J97" t="n">
+      <c r="J97">
         <v>120</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B98" t="s">
         <v>11</v>
       </c>
-      <c r="C98"/>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98"/>
-      <c r="H98"/>
-      <c r="I98"/>
-      <c r="J98"/>
-    </row>
-    <row r="99">
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>143</v>
+      </c>
+      <c r="B99" t="s">
         <v>144</v>
-      </c>
-      <c r="B99" t="s">
-        <v>145</v>
       </c>
       <c r="C99" t="s">
         <v>26</v>
@@ -4217,30 +4217,30 @@
         <v>15</v>
       </c>
       <c r="E99" t="s">
+        <v>144</v>
+      </c>
+      <c r="F99" t="s">
         <v>145</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>146</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99">
+        <v>101940.41</v>
+      </c>
+      <c r="I99" t="s">
         <v>147</v>
       </c>
-      <c r="H99" t="n">
-        <v>101940.41</v>
-      </c>
-      <c r="I99" t="s">
+      <c r="J99">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>148</v>
       </c>
-      <c r="J99" t="n">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>149</v>
-      </c>
       <c r="B100" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -4249,30 +4249,30 @@
         <v>15</v>
       </c>
       <c r="E100" t="s">
+        <v>144</v>
+      </c>
+      <c r="F100" t="s">
         <v>145</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>146</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100">
+        <v>9637.14</v>
+      </c>
+      <c r="I100" t="s">
         <v>147</v>
       </c>
-      <c r="H100" t="n">
-        <v>9637.14</v>
-      </c>
-      <c r="I100" t="s">
-        <v>148</v>
-      </c>
-      <c r="J100" t="n">
+      <c r="J100">
         <v>93</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B101" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C101" t="s">
         <v>26</v>
@@ -4281,30 +4281,30 @@
         <v>20</v>
       </c>
       <c r="E101" t="s">
+        <v>144</v>
+      </c>
+      <c r="F101" t="s">
         <v>145</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>146</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101">
+        <v>220069.98</v>
+      </c>
+      <c r="I101" t="s">
         <v>147</v>
       </c>
-      <c r="H101" t="n">
-        <v>220069.98</v>
-      </c>
-      <c r="I101" t="s">
-        <v>148</v>
-      </c>
-      <c r="J101" t="n">
+      <c r="J101">
         <v>2110</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B102" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
@@ -4313,30 +4313,30 @@
         <v>20</v>
       </c>
       <c r="E102" t="s">
+        <v>144</v>
+      </c>
+      <c r="F102" t="s">
         <v>145</v>
       </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>146</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102">
+        <v>1530.19</v>
+      </c>
+      <c r="I102" t="s">
         <v>147</v>
       </c>
-      <c r="H102" t="n">
-        <v>1530.19</v>
-      </c>
-      <c r="I102" t="s">
-        <v>148</v>
-      </c>
-      <c r="J102" t="n">
+      <c r="J102">
         <v>25</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C103" t="s">
         <v>22</v>
@@ -4345,30 +4345,30 @@
         <v>20</v>
       </c>
       <c r="E103" t="s">
+        <v>144</v>
+      </c>
+      <c r="F103" t="s">
         <v>145</v>
       </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>146</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103">
+        <v>7572.25</v>
+      </c>
+      <c r="I103" t="s">
         <v>147</v>
       </c>
-      <c r="H103" t="n">
-        <v>7572.25</v>
-      </c>
-      <c r="I103" t="s">
-        <v>148</v>
-      </c>
-      <c r="J103" t="n">
+      <c r="J103">
         <v>80</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B104" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C104" t="s">
         <v>26</v>
@@ -4377,30 +4377,30 @@
         <v>23</v>
       </c>
       <c r="E104" t="s">
+        <v>144</v>
+      </c>
+      <c r="F104" t="s">
         <v>145</v>
       </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>146</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104">
+        <v>134653.37</v>
+      </c>
+      <c r="I104" t="s">
         <v>147</v>
       </c>
-      <c r="H104" t="n">
-        <v>134653.37</v>
-      </c>
-      <c r="I104" t="s">
-        <v>148</v>
-      </c>
-      <c r="J104" t="n">
+      <c r="J104">
         <v>1372</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B105" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -4409,30 +4409,30 @@
         <v>23</v>
       </c>
       <c r="E105" t="s">
+        <v>144</v>
+      </c>
+      <c r="F105" t="s">
         <v>145</v>
       </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>146</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105">
+        <v>11387.83</v>
+      </c>
+      <c r="I105" t="s">
         <v>147</v>
       </c>
-      <c r="H105" t="n">
-        <v>11387.83</v>
-      </c>
-      <c r="I105" t="s">
-        <v>148</v>
-      </c>
-      <c r="J105" t="n">
+      <c r="J105">
         <v>109</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C106" t="s">
         <v>26</v>
@@ -4441,30 +4441,30 @@
         <v>28</v>
       </c>
       <c r="E106" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F106" t="s">
         <v>24</v>
       </c>
       <c r="G106" t="s">
+        <v>146</v>
+      </c>
+      <c r="H106">
+        <v>28042.080000000002</v>
+      </c>
+      <c r="I106" t="s">
         <v>147</v>
       </c>
-      <c r="H106" t="n">
-        <v>28042.08</v>
-      </c>
-      <c r="I106" t="s">
-        <v>148</v>
-      </c>
-      <c r="J106" t="n">
+      <c r="J106">
         <v>291</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C107" t="s">
         <v>14</v>
@@ -4473,30 +4473,30 @@
         <v>28</v>
       </c>
       <c r="E107" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F107" t="s">
         <v>24</v>
       </c>
       <c r="G107" t="s">
+        <v>146</v>
+      </c>
+      <c r="H107">
+        <v>3097.11</v>
+      </c>
+      <c r="I107" t="s">
         <v>147</v>
       </c>
-      <c r="H107" t="n">
-        <v>3097.11</v>
-      </c>
-      <c r="I107" t="s">
-        <v>148</v>
-      </c>
-      <c r="J107" t="n">
+      <c r="J107">
         <v>41</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C108" t="s">
         <v>26</v>
@@ -4505,30 +4505,30 @@
         <v>32</v>
       </c>
       <c r="E108" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F108" t="s">
         <v>24</v>
       </c>
       <c r="G108" t="s">
+        <v>146</v>
+      </c>
+      <c r="H108">
+        <v>30220.33</v>
+      </c>
+      <c r="I108" t="s">
         <v>147</v>
       </c>
-      <c r="H108" t="n">
-        <v>30220.33</v>
-      </c>
-      <c r="I108" t="s">
-        <v>148</v>
-      </c>
-      <c r="J108" t="n">
+      <c r="J108">
         <v>286</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C109" t="s">
         <v>22</v>
@@ -4537,30 +4537,30 @@
         <v>32</v>
       </c>
       <c r="E109" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F109" t="s">
         <v>24</v>
       </c>
       <c r="G109" t="s">
+        <v>146</v>
+      </c>
+      <c r="H109">
+        <v>1336.52</v>
+      </c>
+      <c r="I109" t="s">
         <v>147</v>
       </c>
-      <c r="H109" t="n">
-        <v>1336.52</v>
-      </c>
-      <c r="I109" t="s">
-        <v>148</v>
-      </c>
-      <c r="J109" t="n">
+      <c r="J109">
         <v>17</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B110" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C110" t="s">
         <v>26</v>
@@ -4569,30 +4569,30 @@
         <v>38</v>
       </c>
       <c r="E110" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F110" t="s">
         <v>24</v>
       </c>
       <c r="G110" t="s">
+        <v>146</v>
+      </c>
+      <c r="H110">
+        <v>22959.58</v>
+      </c>
+      <c r="I110" t="s">
         <v>147</v>
       </c>
-      <c r="H110" t="n">
-        <v>22959.58</v>
-      </c>
-      <c r="I110" t="s">
-        <v>148</v>
-      </c>
-      <c r="J110" t="n">
+      <c r="J110">
         <v>266</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C111" t="s">
         <v>14</v>
@@ -4601,30 +4601,30 @@
         <v>38</v>
       </c>
       <c r="E111" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F111" t="s">
         <v>24</v>
       </c>
       <c r="G111" t="s">
+        <v>146</v>
+      </c>
+      <c r="H111">
+        <v>1646.9</v>
+      </c>
+      <c r="I111" t="s">
         <v>147</v>
       </c>
-      <c r="H111" t="n">
-        <v>1646.9</v>
-      </c>
-      <c r="I111" t="s">
-        <v>148</v>
-      </c>
-      <c r="J111" t="n">
+      <c r="J111">
         <v>31</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B112" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C112" t="s">
         <v>26</v>
@@ -4633,30 +4633,30 @@
         <v>41</v>
       </c>
       <c r="E112" t="s">
+        <v>144</v>
+      </c>
+      <c r="F112" t="s">
         <v>145</v>
       </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>146</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112">
+        <v>131327</v>
+      </c>
+      <c r="I112" t="s">
         <v>147</v>
       </c>
-      <c r="H112" t="n">
-        <v>131327</v>
-      </c>
-      <c r="I112" t="s">
-        <v>148</v>
-      </c>
-      <c r="J112" t="n">
+      <c r="J112">
         <v>975</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B113" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C113" t="s">
         <v>14</v>
@@ -4665,30 +4665,30 @@
         <v>41</v>
       </c>
       <c r="E113" t="s">
+        <v>144</v>
+      </c>
+      <c r="F113" t="s">
         <v>145</v>
       </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>146</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113">
+        <v>1660.48</v>
+      </c>
+      <c r="I113" t="s">
         <v>147</v>
       </c>
-      <c r="H113" t="n">
-        <v>1660.48</v>
-      </c>
-      <c r="I113" t="s">
-        <v>148</v>
-      </c>
-      <c r="J113" t="n">
+      <c r="J113">
         <v>22</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B114" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C114" t="s">
         <v>22</v>
@@ -4697,30 +4697,30 @@
         <v>41</v>
       </c>
       <c r="E114" t="s">
+        <v>144</v>
+      </c>
+      <c r="F114" t="s">
         <v>145</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
         <v>146</v>
       </c>
-      <c r="G114" t="s">
+      <c r="H114">
+        <v>1040.99</v>
+      </c>
+      <c r="I114" t="s">
         <v>147</v>
       </c>
-      <c r="H114" t="n">
-        <v>1040.99</v>
-      </c>
-      <c r="I114" t="s">
-        <v>148</v>
-      </c>
-      <c r="J114" t="n">
+      <c r="J114">
         <v>21</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B115" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C115" t="s">
         <v>26</v>
@@ -4729,30 +4729,30 @@
         <v>46</v>
       </c>
       <c r="E115" t="s">
+        <v>144</v>
+      </c>
+      <c r="F115" t="s">
         <v>145</v>
       </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>146</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115">
+        <v>119462.26</v>
+      </c>
+      <c r="I115" t="s">
         <v>147</v>
       </c>
-      <c r="H115" t="n">
-        <v>119462.26</v>
-      </c>
-      <c r="I115" t="s">
-        <v>148</v>
-      </c>
-      <c r="J115" t="n">
+      <c r="J115">
         <v>958</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B116" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C116" t="s">
         <v>14</v>
@@ -4761,30 +4761,30 @@
         <v>46</v>
       </c>
       <c r="E116" t="s">
+        <v>144</v>
+      </c>
+      <c r="F116" t="s">
         <v>145</v>
       </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>146</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116">
+        <v>3565.71</v>
+      </c>
+      <c r="I116" t="s">
         <v>147</v>
       </c>
-      <c r="H116" t="n">
-        <v>3565.71</v>
-      </c>
-      <c r="I116" t="s">
-        <v>148</v>
-      </c>
-      <c r="J116" t="n">
+      <c r="J116">
         <v>43</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B117" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
         <v>22</v>
@@ -4793,30 +4793,30 @@
         <v>46</v>
       </c>
       <c r="E117" t="s">
+        <v>144</v>
+      </c>
+      <c r="F117" t="s">
         <v>145</v>
       </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>146</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117">
+        <v>1088.8900000000001</v>
+      </c>
+      <c r="I117" t="s">
         <v>147</v>
       </c>
-      <c r="H117" t="n">
-        <v>1088.89</v>
-      </c>
-      <c r="I117" t="s">
-        <v>148</v>
-      </c>
-      <c r="J117" t="n">
+      <c r="J117">
         <v>27</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C118" t="s">
         <v>26</v>
@@ -4825,30 +4825,30 @@
         <v>49</v>
       </c>
       <c r="E118" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F118" t="s">
         <v>24</v>
       </c>
       <c r="G118" t="s">
-        <v>147</v>
-      </c>
-      <c r="H118" t="n">
+        <v>146</v>
+      </c>
+      <c r="H118">
         <v>17417.59</v>
       </c>
       <c r="I118" t="s">
+        <v>167</v>
+      </c>
+      <c r="J118">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>168</v>
       </c>
-      <c r="J118" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>169</v>
-      </c>
       <c r="B119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C119" t="s">
         <v>22</v>
@@ -4857,30 +4857,30 @@
         <v>49</v>
       </c>
       <c r="E119" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F119" t="s">
         <v>24</v>
       </c>
       <c r="G119" t="s">
-        <v>147</v>
-      </c>
-      <c r="H119" t="n">
+        <v>146</v>
+      </c>
+      <c r="H119">
         <v>47923.07</v>
       </c>
       <c r="I119" t="s">
-        <v>168</v>
-      </c>
-      <c r="J119" t="n">
+        <v>167</v>
+      </c>
+      <c r="J119">
         <v>1146</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B120" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C120" t="s">
         <v>26</v>
@@ -4889,30 +4889,30 @@
         <v>52</v>
       </c>
       <c r="E120" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F120" t="s">
         <v>24</v>
       </c>
       <c r="G120" t="s">
-        <v>147</v>
-      </c>
-      <c r="H120" t="n">
-        <v>19706.65</v>
+        <v>146</v>
+      </c>
+      <c r="H120">
+        <v>19706.650000000001</v>
       </c>
       <c r="I120" t="s">
-        <v>168</v>
-      </c>
-      <c r="J120" t="n">
+        <v>167</v>
+      </c>
+      <c r="J120">
         <v>116</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B121" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C121" t="s">
         <v>22</v>
@@ -4921,30 +4921,30 @@
         <v>52</v>
       </c>
       <c r="E121" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F121" t="s">
         <v>24</v>
       </c>
       <c r="G121" t="s">
-        <v>147</v>
-      </c>
-      <c r="H121" t="n">
+        <v>146</v>
+      </c>
+      <c r="H121">
         <v>43450.17</v>
       </c>
       <c r="I121" t="s">
-        <v>168</v>
-      </c>
-      <c r="J121" t="n">
+        <v>167</v>
+      </c>
+      <c r="J121">
         <v>874</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B122" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C122" t="s">
         <v>26</v>
@@ -4953,30 +4953,30 @@
         <v>55</v>
       </c>
       <c r="E122" t="s">
+        <v>144</v>
+      </c>
+      <c r="F122" t="s">
         <v>145</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>146</v>
       </c>
-      <c r="G122" t="s">
-        <v>147</v>
-      </c>
-      <c r="H122" t="n">
+      <c r="H122">
         <v>43934.26</v>
       </c>
       <c r="I122" t="s">
-        <v>168</v>
-      </c>
-      <c r="J122" t="n">
+        <v>167</v>
+      </c>
+      <c r="J122">
         <v>488</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B123" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C123" t="s">
         <v>14</v>
@@ -4985,30 +4985,30 @@
         <v>55</v>
       </c>
       <c r="E123" t="s">
+        <v>144</v>
+      </c>
+      <c r="F123" t="s">
         <v>145</v>
       </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>146</v>
       </c>
-      <c r="G123" t="s">
-        <v>147</v>
-      </c>
-      <c r="H123" t="n">
+      <c r="H123">
         <v>3098.54</v>
       </c>
       <c r="I123" t="s">
-        <v>168</v>
-      </c>
-      <c r="J123" t="n">
+        <v>167</v>
+      </c>
+      <c r="J123">
         <v>51</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B124" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C124" t="s">
         <v>22</v>
@@ -5017,30 +5017,30 @@
         <v>55</v>
       </c>
       <c r="E124" t="s">
+        <v>144</v>
+      </c>
+      <c r="F124" t="s">
         <v>145</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>146</v>
       </c>
-      <c r="G124" t="s">
-        <v>147</v>
-      </c>
-      <c r="H124" t="n">
+      <c r="H124">
         <v>22431.74</v>
       </c>
       <c r="I124" t="s">
-        <v>168</v>
-      </c>
-      <c r="J124" t="n">
+        <v>167</v>
+      </c>
+      <c r="J124">
         <v>563</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B125" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C125" t="s">
         <v>26</v>
@@ -5049,30 +5049,30 @@
         <v>59</v>
       </c>
       <c r="E125" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F125" t="s">
         <v>24</v>
       </c>
       <c r="G125" t="s">
-        <v>147</v>
-      </c>
-      <c r="H125" t="n">
+        <v>146</v>
+      </c>
+      <c r="H125">
         <v>22997.42</v>
       </c>
       <c r="I125" t="s">
-        <v>168</v>
-      </c>
-      <c r="J125" t="n">
+        <v>167</v>
+      </c>
+      <c r="J125">
         <v>186</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B126" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C126" t="s">
         <v>14</v>
@@ -5081,30 +5081,30 @@
         <v>59</v>
       </c>
       <c r="E126" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F126" t="s">
         <v>24</v>
       </c>
       <c r="G126" t="s">
-        <v>147</v>
-      </c>
-      <c r="H126" t="n">
+        <v>146</v>
+      </c>
+      <c r="H126">
         <v>5881.6</v>
       </c>
       <c r="I126" t="s">
-        <v>168</v>
-      </c>
-      <c r="J126" t="n">
+        <v>167</v>
+      </c>
+      <c r="J126">
         <v>89</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
+        <v>176</v>
+      </c>
+      <c r="B127" t="s">
         <v>177</v>
-      </c>
-      <c r="B127" t="s">
-        <v>178</v>
       </c>
       <c r="C127" t="s">
         <v>26</v>
@@ -5113,7 +5113,7 @@
         <v>15</v>
       </c>
       <c r="E127" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F127" t="s">
         <v>24</v>
@@ -5121,22 +5121,22 @@
       <c r="G127" t="s">
         <v>17</v>
       </c>
-      <c r="H127" t="n">
+      <c r="H127">
         <v>51467.23</v>
       </c>
       <c r="I127" t="s">
+        <v>178</v>
+      </c>
+      <c r="J127">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>179</v>
       </c>
-      <c r="J127" t="n">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>180</v>
-      </c>
       <c r="B128" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C128" t="s">
         <v>22</v>
@@ -5145,7 +5145,7 @@
         <v>15</v>
       </c>
       <c r="E128" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F128" t="s">
         <v>24</v>
@@ -5153,22 +5153,22 @@
       <c r="G128" t="s">
         <v>17</v>
       </c>
-      <c r="H128" t="n">
+      <c r="H128">
         <v>9894.68</v>
       </c>
       <c r="I128" t="s">
-        <v>179</v>
-      </c>
-      <c r="J128" t="n">
+        <v>178</v>
+      </c>
+      <c r="J128">
         <v>156</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B129" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C129" t="s">
         <v>26</v>
@@ -5177,7 +5177,7 @@
         <v>20</v>
       </c>
       <c r="E129" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F129" t="s">
         <v>24</v>
@@ -5185,22 +5185,22 @@
       <c r="G129" t="s">
         <v>17</v>
       </c>
-      <c r="H129" t="n">
-        <v>35922.95</v>
+      <c r="H129">
+        <v>35922.949999999997</v>
       </c>
       <c r="I129" t="s">
-        <v>179</v>
-      </c>
-      <c r="J129" t="n">
+        <v>178</v>
+      </c>
+      <c r="J129">
         <v>239</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B130" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C130" t="s">
         <v>22</v>
@@ -5209,7 +5209,7 @@
         <v>20</v>
       </c>
       <c r="E130" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F130" t="s">
         <v>24</v>
@@ -5217,22 +5217,22 @@
       <c r="G130" t="s">
         <v>17</v>
       </c>
-      <c r="H130" t="n">
-        <v>4729.48</v>
+      <c r="H130">
+        <v>4729.4799999999996</v>
       </c>
       <c r="I130" t="s">
-        <v>179</v>
-      </c>
-      <c r="J130" t="n">
+        <v>178</v>
+      </c>
+      <c r="J130">
         <v>84</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C131" t="s">
         <v>26</v>
@@ -5241,7 +5241,7 @@
         <v>23</v>
       </c>
       <c r="E131" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F131" t="s">
         <v>24</v>
@@ -5249,22 +5249,22 @@
       <c r="G131" t="s">
         <v>17</v>
       </c>
-      <c r="H131" t="n">
+      <c r="H131">
         <v>11799.11</v>
       </c>
       <c r="I131" t="s">
-        <v>179</v>
-      </c>
-      <c r="J131" t="n">
+        <v>178</v>
+      </c>
+      <c r="J131">
         <v>95</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B132" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C132" t="s">
         <v>22</v>
@@ -5273,7 +5273,7 @@
         <v>23</v>
       </c>
       <c r="E132" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F132" t="s">
         <v>24</v>
@@ -5281,22 +5281,22 @@
       <c r="G132" t="s">
         <v>17</v>
       </c>
-      <c r="H132" t="n">
+      <c r="H132">
         <v>1737.75</v>
       </c>
       <c r="I132" t="s">
-        <v>179</v>
-      </c>
-      <c r="J132" t="n">
+        <v>178</v>
+      </c>
+      <c r="J132">
         <v>43</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B133" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C133" t="s">
         <v>14</v>
@@ -5305,7 +5305,7 @@
         <v>28</v>
       </c>
       <c r="E133" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F133" t="s">
         <v>16</v>
@@ -5313,22 +5313,22 @@
       <c r="G133" t="s">
         <v>17</v>
       </c>
-      <c r="H133" t="n">
+      <c r="H133">
         <v>6933.12</v>
       </c>
       <c r="I133" t="s">
-        <v>179</v>
-      </c>
-      <c r="J133" t="n">
+        <v>178</v>
+      </c>
+      <c r="J133">
         <v>101</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C134" t="s">
         <v>22</v>
@@ -5337,7 +5337,7 @@
         <v>28</v>
       </c>
       <c r="E134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F134" t="s">
         <v>16</v>
@@ -5345,22 +5345,22 @@
       <c r="G134" t="s">
         <v>17</v>
       </c>
-      <c r="H134" t="n">
-        <v>4207.39</v>
+      <c r="H134">
+        <v>4207.3900000000003</v>
       </c>
       <c r="I134" t="s">
-        <v>179</v>
-      </c>
-      <c r="J134" t="n">
+        <v>178</v>
+      </c>
+      <c r="J134">
         <v>92</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C135" t="s">
         <v>26</v>
@@ -5369,7 +5369,7 @@
         <v>32</v>
       </c>
       <c r="E135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F135" t="s">
         <v>29</v>
@@ -5377,22 +5377,22 @@
       <c r="G135" t="s">
         <v>17</v>
       </c>
-      <c r="H135" t="n">
+      <c r="H135">
         <v>46705.34</v>
       </c>
       <c r="I135" t="s">
-        <v>179</v>
-      </c>
-      <c r="J135" t="n">
+        <v>178</v>
+      </c>
+      <c r="J135">
         <v>183</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B136" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -5401,7 +5401,7 @@
         <v>32</v>
       </c>
       <c r="E136" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F136" t="s">
         <v>29</v>
@@ -5409,22 +5409,22 @@
       <c r="G136" t="s">
         <v>17</v>
       </c>
-      <c r="H136" t="n">
+      <c r="H136">
         <v>2876.93</v>
       </c>
       <c r="I136" t="s">
-        <v>179</v>
-      </c>
-      <c r="J136" t="n">
+        <v>178</v>
+      </c>
+      <c r="J136">
         <v>48</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B137" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C137" t="s">
         <v>22</v>
@@ -5433,7 +5433,7 @@
         <v>32</v>
       </c>
       <c r="E137" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F137" t="s">
         <v>29</v>
@@ -5441,22 +5441,22 @@
       <c r="G137" t="s">
         <v>17</v>
       </c>
-      <c r="H137" t="n">
+      <c r="H137">
         <v>2379.75</v>
       </c>
       <c r="I137" t="s">
-        <v>179</v>
-      </c>
-      <c r="J137" t="n">
+        <v>178</v>
+      </c>
+      <c r="J137">
         <v>52</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C138" t="s">
         <v>26</v>
@@ -5465,7 +5465,7 @@
         <v>35</v>
       </c>
       <c r="E138" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F138" t="s">
         <v>29</v>
@@ -5473,22 +5473,22 @@
       <c r="G138" t="s">
         <v>17</v>
       </c>
-      <c r="H138" t="n">
+      <c r="H138">
         <v>32678.95</v>
       </c>
       <c r="I138" t="s">
-        <v>179</v>
-      </c>
-      <c r="J138" t="n">
+        <v>178</v>
+      </c>
+      <c r="J138">
         <v>158</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B139" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
@@ -5497,7 +5497,7 @@
         <v>35</v>
       </c>
       <c r="E139" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F139" t="s">
         <v>29</v>
@@ -5505,22 +5505,22 @@
       <c r="G139" t="s">
         <v>17</v>
       </c>
-      <c r="H139" t="n">
+      <c r="H139">
         <v>8218.08</v>
       </c>
       <c r="I139" t="s">
-        <v>179</v>
-      </c>
-      <c r="J139" t="n">
+        <v>178</v>
+      </c>
+      <c r="J139">
         <v>102</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B140" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C140" t="s">
         <v>22</v>
@@ -5529,7 +5529,7 @@
         <v>35</v>
       </c>
       <c r="E140" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F140" t="s">
         <v>29</v>
@@ -5537,22 +5537,22 @@
       <c r="G140" t="s">
         <v>17</v>
       </c>
-      <c r="H140" t="n">
+      <c r="H140">
         <v>706.18</v>
       </c>
       <c r="I140" t="s">
-        <v>179</v>
-      </c>
-      <c r="J140" t="n">
+        <v>178</v>
+      </c>
+      <c r="J140">
         <v>21</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B141" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C141" t="s">
         <v>26</v>
@@ -5561,7 +5561,7 @@
         <v>38</v>
       </c>
       <c r="E141" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F141" t="s">
         <v>29</v>
@@ -5569,22 +5569,22 @@
       <c r="G141" t="s">
         <v>17</v>
       </c>
-      <c r="H141" t="n">
+      <c r="H141">
         <v>59049.22</v>
       </c>
       <c r="I141" t="s">
-        <v>179</v>
-      </c>
-      <c r="J141" t="n">
+        <v>178</v>
+      </c>
+      <c r="J141">
         <v>275</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C142" t="s">
         <v>14</v>
@@ -5593,7 +5593,7 @@
         <v>38</v>
       </c>
       <c r="E142" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F142" t="s">
         <v>29</v>
@@ -5601,22 +5601,22 @@
       <c r="G142" t="s">
         <v>17</v>
       </c>
-      <c r="H142" t="n">
+      <c r="H142">
         <v>3709.09</v>
       </c>
       <c r="I142" t="s">
-        <v>179</v>
-      </c>
-      <c r="J142" t="n">
+        <v>178</v>
+      </c>
+      <c r="J142">
         <v>57</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B143" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C143" t="s">
         <v>22</v>
@@ -5625,7 +5625,7 @@
         <v>38</v>
       </c>
       <c r="E143" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F143" t="s">
         <v>29</v>
@@ -5633,22 +5633,22 @@
       <c r="G143" t="s">
         <v>17</v>
       </c>
-      <c r="H143" t="n">
-        <v>5000.11</v>
+      <c r="H143">
+        <v>5000.1099999999997</v>
       </c>
       <c r="I143" t="s">
-        <v>179</v>
-      </c>
-      <c r="J143" t="n">
+        <v>178</v>
+      </c>
+      <c r="J143">
         <v>117</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B144" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C144" t="s">
         <v>26</v>
@@ -5657,7 +5657,7 @@
         <v>41</v>
       </c>
       <c r="E144" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F144" t="s">
         <v>24</v>
@@ -5665,22 +5665,22 @@
       <c r="G144" t="s">
         <v>17</v>
       </c>
-      <c r="H144" t="n">
+      <c r="H144">
         <v>11652.86</v>
       </c>
       <c r="I144" t="s">
+        <v>196</v>
+      </c>
+      <c r="J144">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
         <v>197</v>
       </c>
-      <c r="J144" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>198</v>
-      </c>
       <c r="B145" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C145" t="s">
         <v>22</v>
@@ -5689,7 +5689,7 @@
         <v>41</v>
       </c>
       <c r="E145" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F145" t="s">
         <v>24</v>
@@ -5697,22 +5697,22 @@
       <c r="G145" t="s">
         <v>17</v>
       </c>
-      <c r="H145" t="n">
+      <c r="H145">
         <v>1882.88</v>
       </c>
       <c r="I145" t="s">
-        <v>197</v>
-      </c>
-      <c r="J145" t="n">
+        <v>196</v>
+      </c>
+      <c r="J145">
         <v>30</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C146" t="s">
         <v>26</v>
@@ -5721,7 +5721,7 @@
         <v>44</v>
       </c>
       <c r="E146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F146" t="s">
         <v>24</v>
@@ -5729,22 +5729,22 @@
       <c r="G146" t="s">
         <v>17</v>
       </c>
-      <c r="H146" t="n">
+      <c r="H146">
         <v>15526.24</v>
       </c>
       <c r="I146" t="s">
-        <v>197</v>
-      </c>
-      <c r="J146" t="n">
+        <v>196</v>
+      </c>
+      <c r="J146">
         <v>147</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B147" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -5753,7 +5753,7 @@
         <v>44</v>
       </c>
       <c r="E147" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F147" t="s">
         <v>24</v>
@@ -5761,22 +5761,22 @@
       <c r="G147" t="s">
         <v>17</v>
       </c>
-      <c r="H147" t="n">
+      <c r="H147">
         <v>5196.49</v>
       </c>
       <c r="I147" t="s">
-        <v>197</v>
-      </c>
-      <c r="J147" t="n">
+        <v>196</v>
+      </c>
+      <c r="J147">
         <v>42</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B148" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C148" t="s">
         <v>26</v>
@@ -5785,7 +5785,7 @@
         <v>46</v>
       </c>
       <c r="E148" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F148" t="s">
         <v>24</v>
@@ -5793,22 +5793,22 @@
       <c r="G148" t="s">
         <v>17</v>
       </c>
-      <c r="H148" t="n">
+      <c r="H148">
         <v>13216.11</v>
       </c>
       <c r="I148" t="s">
-        <v>179</v>
-      </c>
-      <c r="J148" t="n">
+        <v>178</v>
+      </c>
+      <c r="J148">
         <v>94</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B149" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C149" t="s">
         <v>22</v>
@@ -5817,7 +5817,7 @@
         <v>46</v>
       </c>
       <c r="E149" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F149" t="s">
         <v>24</v>
@@ -5825,22 +5825,22 @@
       <c r="G149" t="s">
         <v>17</v>
       </c>
-      <c r="H149" t="n">
+      <c r="H149">
         <v>1593.9</v>
       </c>
       <c r="I149" t="s">
-        <v>179</v>
-      </c>
-      <c r="J149" t="n">
+        <v>178</v>
+      </c>
+      <c r="J149">
         <v>35</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B150" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -5849,7 +5849,7 @@
         <v>49</v>
       </c>
       <c r="E150" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F150" t="s">
         <v>16</v>
@@ -5857,22 +5857,22 @@
       <c r="G150" t="s">
         <v>17</v>
       </c>
-      <c r="H150" t="n">
+      <c r="H150">
         <v>7912.96</v>
       </c>
       <c r="I150" t="s">
-        <v>197</v>
-      </c>
-      <c r="J150" t="n">
+        <v>196</v>
+      </c>
+      <c r="J150">
         <v>103</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B151" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
@@ -5881,7 +5881,7 @@
         <v>52</v>
       </c>
       <c r="E151" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F151" t="s">
         <v>16</v>
@@ -5889,22 +5889,22 @@
       <c r="G151" t="s">
         <v>17</v>
       </c>
-      <c r="H151" t="n">
+      <c r="H151">
         <v>5383.93</v>
       </c>
       <c r="I151" t="s">
-        <v>197</v>
-      </c>
-      <c r="J151" t="n">
+        <v>196</v>
+      </c>
+      <c r="J151">
         <v>82</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B152" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C152" t="s">
         <v>14</v>
@@ -5913,7 +5913,7 @@
         <v>55</v>
       </c>
       <c r="E152" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F152" t="s">
         <v>16</v>
@@ -5921,22 +5921,22 @@
       <c r="G152" t="s">
         <v>17</v>
       </c>
-      <c r="H152" t="n">
+      <c r="H152">
         <v>3865.71</v>
       </c>
       <c r="I152" t="s">
-        <v>197</v>
-      </c>
-      <c r="J152" t="n">
+        <v>196</v>
+      </c>
+      <c r="J152">
         <v>52</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B153" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C153" t="s">
         <v>26</v>
@@ -5945,7 +5945,7 @@
         <v>59</v>
       </c>
       <c r="E153" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F153" t="s">
         <v>29</v>
@@ -5953,22 +5953,22 @@
       <c r="G153" t="s">
         <v>17</v>
       </c>
-      <c r="H153" t="n">
+      <c r="H153">
         <v>44354.01</v>
       </c>
       <c r="I153" t="s">
-        <v>179</v>
-      </c>
-      <c r="J153" t="n">
+        <v>178</v>
+      </c>
+      <c r="J153">
         <v>330</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B154" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
@@ -5977,7 +5977,7 @@
         <v>59</v>
       </c>
       <c r="E154" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F154" t="s">
         <v>29</v>
@@ -5985,22 +5985,22 @@
       <c r="G154" t="s">
         <v>17</v>
       </c>
-      <c r="H154" t="n">
-        <v>2572.3</v>
+      <c r="H154">
+        <v>2572.3000000000002</v>
       </c>
       <c r="I154" t="s">
-        <v>179</v>
-      </c>
-      <c r="J154" t="n">
+        <v>178</v>
+      </c>
+      <c r="J154">
         <v>35</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B155" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C155" t="s">
         <v>22</v>
@@ -6009,7 +6009,7 @@
         <v>59</v>
       </c>
       <c r="E155" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F155" t="s">
         <v>29</v>
@@ -6017,22 +6017,22 @@
       <c r="G155" t="s">
         <v>17</v>
       </c>
-      <c r="H155" t="n">
+      <c r="H155">
         <v>3574.33</v>
       </c>
       <c r="I155" t="s">
-        <v>179</v>
-      </c>
-      <c r="J155" t="n">
+        <v>178</v>
+      </c>
+      <c r="J155">
         <v>88</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C156" t="s">
         <v>14</v>
@@ -6041,7 +6041,7 @@
         <v>62</v>
       </c>
       <c r="E156" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F156" t="s">
         <v>16</v>
@@ -6049,22 +6049,22 @@
       <c r="G156" t="s">
         <v>17</v>
       </c>
-      <c r="H156" t="n">
+      <c r="H156">
         <v>2978.48</v>
       </c>
       <c r="I156" t="s">
-        <v>197</v>
-      </c>
-      <c r="J156" t="n">
+        <v>196</v>
+      </c>
+      <c r="J156">
         <v>41</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
+        <v>209</v>
+      </c>
+      <c r="B157" t="s">
         <v>210</v>
-      </c>
-      <c r="B157" t="s">
-        <v>211</v>
       </c>
       <c r="C157" t="s">
         <v>26</v>
@@ -6073,30 +6073,30 @@
         <v>15</v>
       </c>
       <c r="E157" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F157" t="s">
         <v>29</v>
       </c>
       <c r="G157" t="s">
-        <v>114</v>
-      </c>
-      <c r="H157" t="n">
+        <v>113</v>
+      </c>
+      <c r="H157">
         <v>125079.78</v>
       </c>
       <c r="I157" t="s">
+        <v>211</v>
+      </c>
+      <c r="J157">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
         <v>212</v>
       </c>
-      <c r="J157" t="n">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>213</v>
-      </c>
       <c r="B158" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C158" t="s">
         <v>22</v>
@@ -6105,30 +6105,30 @@
         <v>15</v>
       </c>
       <c r="E158" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F158" t="s">
         <v>29</v>
       </c>
       <c r="G158" t="s">
-        <v>114</v>
-      </c>
-      <c r="H158" t="n">
+        <v>113</v>
+      </c>
+      <c r="H158">
         <v>24791.38</v>
       </c>
       <c r="I158" t="s">
-        <v>212</v>
-      </c>
-      <c r="J158" t="n">
+        <v>211</v>
+      </c>
+      <c r="J158">
         <v>503</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B159" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C159" t="s">
         <v>26</v>
@@ -6137,30 +6137,30 @@
         <v>20</v>
       </c>
       <c r="E159" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F159" t="s">
         <v>29</v>
       </c>
       <c r="G159" t="s">
-        <v>114</v>
-      </c>
-      <c r="H159" t="n">
+        <v>113</v>
+      </c>
+      <c r="H159">
         <v>84640.5</v>
       </c>
       <c r="I159" t="s">
-        <v>212</v>
-      </c>
-      <c r="J159" t="n">
+        <v>211</v>
+      </c>
+      <c r="J159">
         <v>898</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B160" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C160" t="s">
         <v>22</v>
@@ -6169,30 +6169,30 @@
         <v>20</v>
       </c>
       <c r="E160" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F160" t="s">
         <v>29</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
-      </c>
-      <c r="H160" t="n">
+        <v>113</v>
+      </c>
+      <c r="H160">
         <v>15098.51</v>
       </c>
       <c r="I160" t="s">
-        <v>212</v>
-      </c>
-      <c r="J160" t="n">
+        <v>211</v>
+      </c>
+      <c r="J160">
         <v>226</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C161" t="s">
         <v>26</v>
@@ -6201,30 +6201,30 @@
         <v>23</v>
       </c>
       <c r="E161" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F161" t="s">
         <v>29</v>
       </c>
       <c r="G161" t="s">
-        <v>114</v>
-      </c>
-      <c r="H161" t="n">
+        <v>113</v>
+      </c>
+      <c r="H161">
         <v>106227.95</v>
       </c>
       <c r="I161" t="s">
-        <v>212</v>
-      </c>
-      <c r="J161" t="n">
+        <v>211</v>
+      </c>
+      <c r="J161">
         <v>1394</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B162" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C162" t="s">
         <v>22</v>
@@ -6233,30 +6233,30 @@
         <v>23</v>
       </c>
       <c r="E162" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F162" t="s">
         <v>29</v>
       </c>
       <c r="G162" t="s">
-        <v>114</v>
-      </c>
-      <c r="H162" t="n">
-        <v>2321.47</v>
+        <v>113</v>
+      </c>
+      <c r="H162">
+        <v>2321.4699999999998</v>
       </c>
       <c r="I162" t="s">
-        <v>212</v>
-      </c>
-      <c r="J162" t="n">
+        <v>211</v>
+      </c>
+      <c r="J162">
         <v>46</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B163" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C163" t="s">
         <v>26</v>
@@ -6265,30 +6265,30 @@
         <v>28</v>
       </c>
       <c r="E163" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F163" t="s">
         <v>29</v>
       </c>
       <c r="G163" t="s">
-        <v>114</v>
-      </c>
-      <c r="H163" t="n">
+        <v>113</v>
+      </c>
+      <c r="H163">
         <v>176685.59</v>
       </c>
       <c r="I163" t="s">
-        <v>212</v>
-      </c>
-      <c r="J163" t="n">
+        <v>211</v>
+      </c>
+      <c r="J163">
         <v>1687</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B164" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C164" t="s">
         <v>22</v>
@@ -6297,30 +6297,30 @@
         <v>28</v>
       </c>
       <c r="E164" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F164" t="s">
         <v>29</v>
       </c>
       <c r="G164" t="s">
-        <v>114</v>
-      </c>
-      <c r="H164" t="n">
+        <v>113</v>
+      </c>
+      <c r="H164">
         <v>20098.3</v>
       </c>
       <c r="I164" t="s">
-        <v>212</v>
-      </c>
-      <c r="J164" t="n">
+        <v>211</v>
+      </c>
+      <c r="J164">
         <v>338</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B165" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C165" t="s">
         <v>14</v>
@@ -6329,30 +6329,30 @@
         <v>35</v>
       </c>
       <c r="E165" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F165" t="s">
         <v>16</v>
       </c>
       <c r="G165" t="s">
-        <v>114</v>
-      </c>
-      <c r="H165" t="n">
+        <v>113</v>
+      </c>
+      <c r="H165">
         <v>2385.98</v>
       </c>
       <c r="I165" t="s">
+        <v>220</v>
+      </c>
+      <c r="J165">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
         <v>221</v>
       </c>
-      <c r="J165" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>222</v>
-      </c>
       <c r="B166" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C166" t="s">
         <v>22</v>
@@ -6361,30 +6361,30 @@
         <v>35</v>
       </c>
       <c r="E166" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F166" t="s">
         <v>16</v>
       </c>
       <c r="G166" t="s">
-        <v>114</v>
-      </c>
-      <c r="H166" t="n">
+        <v>113</v>
+      </c>
+      <c r="H166">
         <v>2694.28</v>
       </c>
       <c r="I166" t="s">
-        <v>221</v>
-      </c>
-      <c r="J166" t="n">
+        <v>220</v>
+      </c>
+      <c r="J166">
         <v>46</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B167" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C167" t="s">
         <v>14</v>
@@ -6393,30 +6393,30 @@
         <v>38</v>
       </c>
       <c r="E167" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F167" t="s">
         <v>16</v>
       </c>
       <c r="G167" t="s">
-        <v>114</v>
-      </c>
-      <c r="H167" t="n">
+        <v>113</v>
+      </c>
+      <c r="H167">
         <v>1838.5</v>
       </c>
       <c r="I167" t="s">
-        <v>221</v>
-      </c>
-      <c r="J167" t="n">
+        <v>220</v>
+      </c>
+      <c r="J167">
         <v>18</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B168" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C168" t="s">
         <v>22</v>
@@ -6425,30 +6425,30 @@
         <v>38</v>
       </c>
       <c r="E168" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F168" t="s">
         <v>16</v>
       </c>
       <c r="G168" t="s">
-        <v>114</v>
-      </c>
-      <c r="H168" t="n">
+        <v>113</v>
+      </c>
+      <c r="H168">
         <v>4074.23</v>
       </c>
       <c r="I168" t="s">
-        <v>221</v>
-      </c>
-      <c r="J168" t="n">
+        <v>220</v>
+      </c>
+      <c r="J168">
         <v>76</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B169" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C169" t="s">
         <v>26</v>
@@ -6457,30 +6457,30 @@
         <v>41</v>
       </c>
       <c r="E169" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F169" t="s">
         <v>24</v>
       </c>
       <c r="G169" t="s">
-        <v>114</v>
-      </c>
-      <c r="H169" t="n">
+        <v>113</v>
+      </c>
+      <c r="H169">
         <v>10218.15</v>
       </c>
       <c r="I169" t="s">
-        <v>221</v>
-      </c>
-      <c r="J169" t="n">
+        <v>220</v>
+      </c>
+      <c r="J169">
         <v>124</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B170" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C170" t="s">
         <v>14</v>
@@ -6489,30 +6489,30 @@
         <v>41</v>
       </c>
       <c r="E170" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F170" t="s">
         <v>24</v>
       </c>
       <c r="G170" t="s">
-        <v>114</v>
-      </c>
-      <c r="H170" t="n">
+        <v>113</v>
+      </c>
+      <c r="H170">
         <v>7515.57</v>
       </c>
       <c r="I170" t="s">
-        <v>221</v>
-      </c>
-      <c r="J170" t="n">
+        <v>220</v>
+      </c>
+      <c r="J170">
         <v>70</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B171" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C171" t="s">
         <v>22</v>
@@ -6521,30 +6521,30 @@
         <v>41</v>
       </c>
       <c r="E171" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F171" t="s">
         <v>24</v>
       </c>
       <c r="G171" t="s">
-        <v>114</v>
-      </c>
-      <c r="H171" t="n">
+        <v>113</v>
+      </c>
+      <c r="H171">
         <v>1756.75</v>
       </c>
       <c r="I171" t="s">
-        <v>221</v>
-      </c>
-      <c r="J171" t="n">
+        <v>220</v>
+      </c>
+      <c r="J171">
         <v>32</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B172" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C172" t="s">
         <v>26</v>
@@ -6553,30 +6553,30 @@
         <v>44</v>
       </c>
       <c r="E172" t="s">
+        <v>210</v>
+      </c>
+      <c r="F172" t="s">
+        <v>24</v>
+      </c>
+      <c r="G172" t="s">
+        <v>113</v>
+      </c>
+      <c r="H172">
+        <v>19420.22</v>
+      </c>
+      <c r="I172" t="s">
         <v>211</v>
       </c>
-      <c r="F172" t="s">
-        <v>24</v>
-      </c>
-      <c r="G172" t="s">
-        <v>114</v>
-      </c>
-      <c r="H172" t="n">
-        <v>19420.22</v>
-      </c>
-      <c r="I172" t="s">
-        <v>212</v>
-      </c>
-      <c r="J172" t="n">
+      <c r="J172">
         <v>298</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B173" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C173" t="s">
         <v>26</v>
@@ -6585,30 +6585,30 @@
         <v>46</v>
       </c>
       <c r="E173" t="s">
+        <v>210</v>
+      </c>
+      <c r="F173" t="s">
+        <v>24</v>
+      </c>
+      <c r="G173" t="s">
+        <v>113</v>
+      </c>
+      <c r="H173">
+        <v>25521.19</v>
+      </c>
+      <c r="I173" t="s">
         <v>211</v>
       </c>
-      <c r="F173" t="s">
-        <v>24</v>
-      </c>
-      <c r="G173" t="s">
-        <v>114</v>
-      </c>
-      <c r="H173" t="n">
-        <v>25521.19</v>
-      </c>
-      <c r="I173" t="s">
-        <v>212</v>
-      </c>
-      <c r="J173" t="n">
+      <c r="J173">
         <v>346</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B174" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C174" t="s">
         <v>26</v>
@@ -6617,30 +6617,30 @@
         <v>49</v>
       </c>
       <c r="E174" t="s">
+        <v>210</v>
+      </c>
+      <c r="F174" t="s">
+        <v>24</v>
+      </c>
+      <c r="G174" t="s">
+        <v>113</v>
+      </c>
+      <c r="H174">
+        <v>22155.85</v>
+      </c>
+      <c r="I174" t="s">
         <v>211</v>
       </c>
-      <c r="F174" t="s">
-        <v>24</v>
-      </c>
-      <c r="G174" t="s">
-        <v>114</v>
-      </c>
-      <c r="H174" t="n">
-        <v>22155.85</v>
-      </c>
-      <c r="I174" t="s">
-        <v>212</v>
-      </c>
-      <c r="J174" t="n">
+      <c r="J174">
         <v>292</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B175" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C175" t="s">
         <v>22</v>
@@ -6649,30 +6649,30 @@
         <v>52</v>
       </c>
       <c r="E175" t="s">
+        <v>210</v>
+      </c>
+      <c r="F175" t="s">
+        <v>24</v>
+      </c>
+      <c r="G175" t="s">
+        <v>113</v>
+      </c>
+      <c r="H175">
+        <v>2325.3000000000002</v>
+      </c>
+      <c r="I175" t="s">
         <v>211</v>
       </c>
-      <c r="F175" t="s">
-        <v>24</v>
-      </c>
-      <c r="G175" t="s">
-        <v>114</v>
-      </c>
-      <c r="H175" t="n">
-        <v>2325.3</v>
-      </c>
-      <c r="I175" t="s">
-        <v>212</v>
-      </c>
-      <c r="J175" t="n">
+      <c r="J175">
         <v>57</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B176" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C176" t="s">
         <v>22</v>
@@ -6681,30 +6681,30 @@
         <v>55</v>
       </c>
       <c r="E176" t="s">
+        <v>210</v>
+      </c>
+      <c r="F176" t="s">
+        <v>24</v>
+      </c>
+      <c r="G176" t="s">
+        <v>113</v>
+      </c>
+      <c r="H176">
+        <v>3476.14</v>
+      </c>
+      <c r="I176" t="s">
         <v>211</v>
       </c>
-      <c r="F176" t="s">
-        <v>24</v>
-      </c>
-      <c r="G176" t="s">
-        <v>114</v>
-      </c>
-      <c r="H176" t="n">
-        <v>3476.14</v>
-      </c>
-      <c r="I176" t="s">
-        <v>212</v>
-      </c>
-      <c r="J176" t="n">
+      <c r="J176">
         <v>67</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B177" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C177" t="s">
         <v>22</v>
@@ -6713,30 +6713,30 @@
         <v>59</v>
       </c>
       <c r="E177" t="s">
+        <v>210</v>
+      </c>
+      <c r="F177" t="s">
+        <v>24</v>
+      </c>
+      <c r="G177" t="s">
+        <v>113</v>
+      </c>
+      <c r="H177">
+        <v>1947.23</v>
+      </c>
+      <c r="I177" t="s">
         <v>211</v>
       </c>
-      <c r="F177" t="s">
-        <v>24</v>
-      </c>
-      <c r="G177" t="s">
-        <v>114</v>
-      </c>
-      <c r="H177" t="n">
-        <v>1947.23</v>
-      </c>
-      <c r="I177" t="s">
-        <v>212</v>
-      </c>
-      <c r="J177" t="n">
+      <c r="J177">
         <v>50</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
+        <v>233</v>
+      </c>
+      <c r="B178" t="s">
         <v>234</v>
-      </c>
-      <c r="B178" t="s">
-        <v>235</v>
       </c>
       <c r="C178" t="s">
         <v>14</v>
@@ -6745,30 +6745,30 @@
         <v>15</v>
       </c>
       <c r="E178" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F178" t="s">
         <v>16</v>
       </c>
       <c r="G178" t="s">
-        <v>66</v>
-      </c>
-      <c r="H178" t="n">
+        <v>252</v>
+      </c>
+      <c r="H178">
         <v>6708.16</v>
       </c>
       <c r="I178" t="s">
+        <v>235</v>
+      </c>
+      <c r="J178">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
         <v>236</v>
       </c>
-      <c r="J178" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>237</v>
-      </c>
       <c r="B179" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C179" t="s">
         <v>22</v>
@@ -6777,30 +6777,30 @@
         <v>15</v>
       </c>
       <c r="E179" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F179" t="s">
         <v>16</v>
       </c>
       <c r="G179" t="s">
-        <v>66</v>
-      </c>
-      <c r="H179" t="n">
-        <v>5099.1</v>
+        <v>252</v>
+      </c>
+      <c r="H179">
+        <v>5099.1000000000004</v>
       </c>
       <c r="I179" t="s">
-        <v>236</v>
-      </c>
-      <c r="J179" t="n">
+        <v>235</v>
+      </c>
+      <c r="J179">
         <v>94</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B180" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C180" t="s">
         <v>14</v>
@@ -6809,30 +6809,30 @@
         <v>20</v>
       </c>
       <c r="E180" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F180" t="s">
         <v>16</v>
       </c>
       <c r="G180" t="s">
-        <v>66</v>
-      </c>
-      <c r="H180" t="n">
-        <v>9250.13</v>
+        <v>252</v>
+      </c>
+      <c r="H180">
+        <v>9250.1299999999992</v>
       </c>
       <c r="I180" t="s">
-        <v>236</v>
-      </c>
-      <c r="J180" t="n">
+        <v>235</v>
+      </c>
+      <c r="J180">
         <v>137</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B181" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C181" t="s">
         <v>14</v>
@@ -6841,30 +6841,30 @@
         <v>23</v>
       </c>
       <c r="E181" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F181" t="s">
         <v>16</v>
       </c>
       <c r="G181" t="s">
-        <v>66</v>
-      </c>
-      <c r="H181" t="n">
-        <v>5103.73</v>
+        <v>252</v>
+      </c>
+      <c r="H181">
+        <v>5103.7299999999996</v>
       </c>
       <c r="I181" t="s">
-        <v>236</v>
-      </c>
-      <c r="J181" t="n">
+        <v>235</v>
+      </c>
+      <c r="J181">
         <v>44</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B182" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C182" t="s">
         <v>26</v>
@@ -6873,30 +6873,30 @@
         <v>28</v>
       </c>
       <c r="E182" t="s">
+        <v>234</v>
+      </c>
+      <c r="F182" t="s">
+        <v>24</v>
+      </c>
+      <c r="G182" t="s">
+        <v>252</v>
+      </c>
+      <c r="H182">
+        <v>39922.300000000003</v>
+      </c>
+      <c r="I182" t="s">
         <v>235</v>
       </c>
-      <c r="F182" t="s">
-        <v>24</v>
-      </c>
-      <c r="G182" t="s">
-        <v>66</v>
-      </c>
-      <c r="H182" t="n">
-        <v>39922.3</v>
-      </c>
-      <c r="I182" t="s">
-        <v>236</v>
-      </c>
-      <c r="J182" t="n">
+      <c r="J182">
         <v>177</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B183" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C183" t="s">
         <v>26</v>
@@ -6905,30 +6905,30 @@
         <v>32</v>
       </c>
       <c r="E183" t="s">
+        <v>234</v>
+      </c>
+      <c r="F183" t="s">
+        <v>24</v>
+      </c>
+      <c r="G183" t="s">
+        <v>252</v>
+      </c>
+      <c r="H183">
+        <v>17356.599999999999</v>
+      </c>
+      <c r="I183" t="s">
         <v>235</v>
       </c>
-      <c r="F183" t="s">
-        <v>24</v>
-      </c>
-      <c r="G183" t="s">
-        <v>66</v>
-      </c>
-      <c r="H183" t="n">
-        <v>17356.6</v>
-      </c>
-      <c r="I183" t="s">
-        <v>236</v>
-      </c>
-      <c r="J183" t="n">
+      <c r="J183">
         <v>110</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B184" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C184" t="s">
         <v>14</v>
@@ -6937,30 +6937,30 @@
         <v>32</v>
       </c>
       <c r="E184" t="s">
+        <v>234</v>
+      </c>
+      <c r="F184" t="s">
+        <v>24</v>
+      </c>
+      <c r="G184" t="s">
+        <v>252</v>
+      </c>
+      <c r="H184">
+        <v>17143.61</v>
+      </c>
+      <c r="I184" t="s">
         <v>235</v>
       </c>
-      <c r="F184" t="s">
-        <v>24</v>
-      </c>
-      <c r="G184" t="s">
-        <v>66</v>
-      </c>
-      <c r="H184" t="n">
-        <v>17143.61</v>
-      </c>
-      <c r="I184" t="s">
-        <v>236</v>
-      </c>
-      <c r="J184" t="n">
+      <c r="J184">
         <v>120</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B185" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C185" t="s">
         <v>22</v>
@@ -6969,30 +6969,30 @@
         <v>32</v>
       </c>
       <c r="E185" t="s">
+        <v>234</v>
+      </c>
+      <c r="F185" t="s">
+        <v>24</v>
+      </c>
+      <c r="G185" t="s">
+        <v>252</v>
+      </c>
+      <c r="H185">
+        <v>3875.61</v>
+      </c>
+      <c r="I185" t="s">
         <v>235</v>
       </c>
-      <c r="F185" t="s">
-        <v>24</v>
-      </c>
-      <c r="G185" t="s">
-        <v>66</v>
-      </c>
-      <c r="H185" t="n">
-        <v>3875.61</v>
-      </c>
-      <c r="I185" t="s">
-        <v>236</v>
-      </c>
-      <c r="J185" t="n">
+      <c r="J185">
         <v>63</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B186" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C186" t="s">
         <v>26</v>
@@ -7001,30 +7001,30 @@
         <v>35</v>
       </c>
       <c r="E186" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F186" t="s">
         <v>24</v>
       </c>
       <c r="G186" t="s">
-        <v>66</v>
-      </c>
-      <c r="H186" t="n">
+        <v>252</v>
+      </c>
+      <c r="H186">
         <v>7905.46</v>
       </c>
       <c r="I186" t="s">
+        <v>244</v>
+      </c>
+      <c r="J186">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
         <v>245</v>
       </c>
-      <c r="J186" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>246</v>
-      </c>
       <c r="B187" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C187" t="s">
         <v>26</v>
@@ -7033,30 +7033,30 @@
         <v>38</v>
       </c>
       <c r="E187" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F187" t="s">
         <v>24</v>
       </c>
       <c r="G187" t="s">
-        <v>66</v>
-      </c>
-      <c r="H187" t="n">
+        <v>252</v>
+      </c>
+      <c r="H187">
         <v>7462.88</v>
       </c>
       <c r="I187" t="s">
-        <v>245</v>
-      </c>
-      <c r="J187" t="n">
+        <v>244</v>
+      </c>
+      <c r="J187">
         <v>54</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B188" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C188" t="s">
         <v>26</v>
@@ -7065,30 +7065,30 @@
         <v>41</v>
       </c>
       <c r="E188" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F188" t="s">
         <v>24</v>
       </c>
       <c r="G188" t="s">
-        <v>66</v>
-      </c>
-      <c r="H188" t="n">
+        <v>252</v>
+      </c>
+      <c r="H188">
         <v>11856.59</v>
       </c>
       <c r="I188" t="s">
-        <v>245</v>
-      </c>
-      <c r="J188" t="n">
+        <v>244</v>
+      </c>
+      <c r="J188">
         <v>105</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C189" t="s">
         <v>14</v>
@@ -7097,30 +7097,30 @@
         <v>46</v>
       </c>
       <c r="E189" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F189" t="s">
         <v>16</v>
       </c>
       <c r="G189" t="s">
-        <v>66</v>
-      </c>
-      <c r="H189" t="n">
-        <v>9322.29</v>
+        <v>252</v>
+      </c>
+      <c r="H189">
+        <v>9322.2900000000009</v>
       </c>
       <c r="I189" t="s">
-        <v>236</v>
-      </c>
-      <c r="J189" t="n">
+        <v>235</v>
+      </c>
+      <c r="J189">
         <v>74</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B190" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C190" t="s">
         <v>22</v>
@@ -7129,30 +7129,30 @@
         <v>46</v>
       </c>
       <c r="E190" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F190" t="s">
         <v>16</v>
       </c>
       <c r="G190" t="s">
-        <v>66</v>
-      </c>
-      <c r="H190" t="n">
+        <v>252</v>
+      </c>
+      <c r="H190">
         <v>6722.85</v>
       </c>
       <c r="I190" t="s">
-        <v>236</v>
-      </c>
-      <c r="J190" t="n">
+        <v>235</v>
+      </c>
+      <c r="J190">
         <v>76</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B191" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C191" t="s">
         <v>14</v>
@@ -7161,30 +7161,30 @@
         <v>49</v>
       </c>
       <c r="E191" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F191" t="s">
         <v>16</v>
       </c>
       <c r="G191" t="s">
-        <v>66</v>
-      </c>
-      <c r="H191" t="n">
+        <v>252</v>
+      </c>
+      <c r="H191">
         <v>26541.74</v>
       </c>
       <c r="I191" t="s">
-        <v>236</v>
-      </c>
-      <c r="J191" t="n">
+        <v>235</v>
+      </c>
+      <c r="J191">
         <v>281</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B192" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C192" t="s">
         <v>22</v>
@@ -7193,30 +7193,30 @@
         <v>49</v>
       </c>
       <c r="E192" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F192" t="s">
         <v>16</v>
       </c>
       <c r="G192" t="s">
-        <v>66</v>
-      </c>
-      <c r="H192" t="n">
+        <v>252</v>
+      </c>
+      <c r="H192">
         <v>23538.36</v>
       </c>
       <c r="I192" t="s">
-        <v>236</v>
-      </c>
-      <c r="J192" t="n">
+        <v>235</v>
+      </c>
+      <c r="J192">
         <v>272</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B193" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C193" t="s">
         <v>14</v>
@@ -7225,26 +7225,26 @@
         <v>52</v>
       </c>
       <c r="E193" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F193" t="s">
         <v>16</v>
       </c>
       <c r="G193" t="s">
-        <v>66</v>
-      </c>
-      <c r="H193" t="n">
+        <v>252</v>
+      </c>
+      <c r="H193">
         <v>3960.23</v>
       </c>
       <c r="I193" t="s">
-        <v>236</v>
-      </c>
-      <c r="J193" t="n">
+        <v>235</v>
+      </c>
+      <c r="J193">
         <v>34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>